--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,22 +591,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -676,22 +676,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -795,31 +795,31 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,17 +846,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -884,27 +884,27 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1016,17 +1016,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,17 +1101,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1139,27 +1139,27 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,22 +1186,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1224,27 +1224,27 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,22 +1271,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1305,26 +1305,26 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,22 +1356,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1390,31 +1390,31 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1424,10 +1424,14 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
+          <t>ATHLETIC BREWING CO</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>ATHLETIC BREWING COMPANY</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1437,17 +1441,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1475,27 +1479,27 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1505,12 +1509,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1522,17 +1526,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1560,27 +1564,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1590,12 +1594,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -1607,22 +1611,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1645,27 +1649,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1675,12 +1679,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1692,22 +1696,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1730,27 +1734,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1777,22 +1781,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1815,27 +1819,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1845,12 +1849,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1862,22 +1866,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1896,31 +1900,31 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1930,12 +1934,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -1947,22 +1951,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,22 +1989,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2015,14 +2019,10 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>CONSTELLATION BRANDS</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2032,22 +2032,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2070,22 +2070,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2117,22 +2117,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2155,22 +2155,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2202,22 +2202,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2240,22 +2240,22 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2287,22 +2287,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2372,22 +2372,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2410,22 +2410,22 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2457,22 +2457,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2495,22 +2495,22 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2542,22 +2542,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -2627,22 +2627,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2665,22 +2665,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2712,12 +2712,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2797,12 +2797,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2835,22 +2835,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3137,83 +3137,678 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>81006</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>21-00 MAPLE AVE</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Ashley Furman</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Feature Activation</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>Cooler Door Wrap</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
+      <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -3252,6 +3847,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3296,7 +3898,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
     </row>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -625,26 +625,26 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -761,12 +761,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -799,22 +799,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,22 +1186,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,12 +1271,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1309,27 +1309,27 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1356,22 +1356,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1390,26 +1390,26 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -1951,22 +1951,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,31 +1985,31 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2019,10 +2019,14 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n"/>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2032,22 +2036,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2070,22 +2074,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2100,14 +2104,10 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2202,22 +2202,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2240,22 +2240,22 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -2372,12 +2372,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2542,12 +2542,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2627,22 +2627,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2665,22 +2665,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2712,12 +2712,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2797,12 +2797,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3137,12 +3137,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3222,22 +3222,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3392,12 +3392,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -3477,12 +3477,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:29 AM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -3732,83 +3732,168 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Ashley Furman</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Feature Activation</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>Cooler Door Wrap</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr">
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -3854,6 +3939,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -625,26 +625,26 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -676,17 +676,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -714,22 +714,22 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -799,22 +799,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,17 +846,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -969,22 +969,22 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1016,12 +1016,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1050,26 +1050,26 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,12 +1101,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,22 +1271,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1309,22 +1309,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,22 +1356,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1394,27 +1394,27 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1441,17 +1441,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1475,31 +1475,31 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1526,17 +1526,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1564,27 +1564,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -1611,17 +1611,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1649,27 +1649,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1696,22 +1696,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1734,27 +1734,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2036,22 +2036,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2074,27 +2074,27 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2104,10 +2104,14 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n"/>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2117,17 +2121,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2155,27 +2159,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2202,17 +2206,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2240,27 +2244,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2270,12 +2274,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -2287,22 +2291,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2325,27 +2329,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2355,12 +2359,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -2372,22 +2376,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2406,31 +2410,31 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2440,12 +2444,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2457,22 +2461,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2495,22 +2499,22 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2525,14 +2529,10 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>VINAIO IMPORTS LTD</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2542,22 +2542,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -2627,22 +2627,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2665,22 +2665,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2712,22 +2712,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2797,22 +2797,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2835,22 +2835,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2882,22 +2882,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2967,22 +2967,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3052,22 +3052,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3222,12 +3222,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3392,12 +3392,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3430,22 +3430,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -3477,12 +3477,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3515,22 +3515,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3732,22 +3732,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3770,22 +3770,22 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3817,83 +3817,508 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Ashley Furman</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Feature Activation</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Cooler Door Wrap</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="inlineStr">
+      <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -3940,6 +4365,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1016,17 +1016,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1050,26 +1050,26 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,12 +1271,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1309,22 +1309,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1649,22 +1649,22 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1696,22 +1696,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1781,12 +1781,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1819,27 +1819,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1866,22 +1866,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1900,26 +1900,26 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2461,22 +2461,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2495,31 +2495,31 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2529,10 +2529,14 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n"/>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2542,22 +2546,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2580,22 +2584,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2610,14 +2614,10 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2712,22 +2712,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2967,12 +2967,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3137,22 +3137,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3175,22 +3175,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3222,12 +3222,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3392,12 +3392,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3732,22 +3732,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3770,22 +3770,22 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3817,22 +3817,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -3987,12 +3987,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:29 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4242,83 +4242,168 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Ashley Furman</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Feature Activation</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>Cooler Door Wrap</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q45" s="3" t="inlineStr">
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -4370,6 +4455,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -629,27 +629,27 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -714,22 +714,22 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1101,17 +1101,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,12 +1271,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1309,17 +1309,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,12 +1356,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1866,12 +1866,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1904,27 +1904,27 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1951,22 +1951,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,26 +1985,26 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2546,22 +2546,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2580,31 +2580,31 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2614,10 +2614,14 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n"/>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2627,22 +2631,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2665,22 +2669,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2695,14 +2699,10 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2797,22 +2797,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2835,22 +2835,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2967,12 +2967,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3137,12 +3137,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3222,22 +3222,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3392,12 +3392,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -3477,12 +3477,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3732,12 +3732,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3817,22 +3817,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3902,22 +3902,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3940,22 +3940,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -3987,12 +3987,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4072,12 +4072,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:29 AM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -4327,83 +4327,168 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Ashley Furman</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Feature Activation</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>Cooler Door Wrap</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
+      <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -4456,6 +4541,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
     </row>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -676,17 +676,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -761,22 +761,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -799,27 +799,27 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,22 +846,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1016,22 +1016,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1101,22 +1101,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,22 +1186,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1220,26 +1220,26 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,22 +1271,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1305,26 +1305,26 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,22 +1356,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1394,27 +1394,27 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1441,22 +1441,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1526,22 +1526,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1564,22 +1564,22 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1594,14 +1594,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>CONSTELLATION BRANDS</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1611,22 +1607,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1649,27 +1645,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1679,12 +1675,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1696,22 +1692,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1734,22 +1730,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1764,12 +1760,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1781,22 +1777,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1819,22 +1815,22 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1849,12 +1845,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1866,17 +1862,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1904,17 +1900,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1924,7 +1920,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1951,17 +1947,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1989,27 +1985,27 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2036,22 +2032,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2070,31 +2066,31 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2104,12 +2100,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2121,22 +2117,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2159,27 +2155,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2189,12 +2185,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2206,22 +2202,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2244,27 +2240,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2274,12 +2270,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -2291,22 +2287,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2329,27 +2325,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2359,12 +2355,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -2376,22 +2372,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2414,27 +2410,27 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2444,12 +2440,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2461,12 +2457,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2495,26 +2491,26 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2529,12 +2525,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2546,22 +2542,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2580,31 +2576,31 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2614,12 +2610,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -2631,22 +2627,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2669,27 +2665,27 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2699,10 +2695,14 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2712,22 +2712,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2750,27 +2750,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2797,22 +2797,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2835,22 +2835,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2882,22 +2882,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2967,22 +2967,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3052,22 +3052,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3137,22 +3137,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3175,22 +3175,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3222,22 +3222,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3341,26 +3341,26 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3430,22 +3430,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -3477,22 +3477,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3515,22 +3515,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3562,22 +3562,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3647,22 +3647,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -3732,22 +3732,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3770,22 +3770,22 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3817,22 +3817,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -3902,17 +3902,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3940,22 +3940,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -3987,22 +3987,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4025,22 +4025,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4072,22 +4072,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4110,27 +4110,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4191,31 +4191,31 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4242,22 +4242,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4280,27 +4280,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4327,22 +4327,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4365,27 +4365,27 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4412,83 +4412,2204 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>09/09/2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>230412</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>17 HAMPTON HOUSE ROAD</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>NEWTON</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>230412</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>17 HAMPTON HOUSE ROAD</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>NEWTON</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>230412</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>17 HAMPTON HOUSE ROAD</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>NEWTON</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>230412</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>17 HAMPTON HOUSE ROAD</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>NEWTON</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>WINELAND</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>50020</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>247 DEGRAW AVE</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>TEANECK</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>WALDWICK WINE/SPIRITS</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>88005</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>23 WYCKOFF AVE</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>WALDWICK</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>WALDWICK WINE/SPIRITS</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>88005</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>23 WYCKOFF AVE</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>WALDWICK</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 12:17 PM</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>20080</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>390 MAIN ST</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>THE LIQUOR SHOP</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>21033</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>498 E 30TH STREET</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>MODELO CHELADA</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>THE LIQUOR SHOP</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>21033</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>498 E 30TH STREET</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>VINAIO IMPORTS LTD</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>THE LIQUOR SHOP</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>21033</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>498 E 30TH STREET</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ORO</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>THE LIQUOR SHOP</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>21033</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>498 E 30TH STREET</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>TRULY HARD SELTZER</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>81006</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>21-00 MAPLE AVE</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q47" s="3" t="inlineStr">
+      <c r="Q72" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -4542,6 +6663,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -710,21 +710,21 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -965,31 +965,31 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -999,14 +999,10 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1016,7 +1012,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1026,12 +1022,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1050,31 +1046,31 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1084,12 +1080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,7 +1097,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1111,12 +1107,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1135,31 +1131,31 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1169,12 +1165,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,22 +1182,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1220,31 +1216,31 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1254,7 +1250,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1271,22 +1267,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1305,31 +1301,31 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1339,7 +1335,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1356,22 +1352,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1390,31 +1386,31 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1424,12 +1420,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1441,22 +1437,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1475,31 +1471,31 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1509,12 +1505,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1526,17 +1522,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1560,31 +1556,31 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1594,10 +1590,14 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1607,22 +1607,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1645,27 +1645,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1692,17 +1692,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1726,31 +1726,31 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1845,14 +1845,10 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1862,12 +1858,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1900,22 +1896,22 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1947,12 +1943,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1985,27 +1981,27 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2032,12 +2028,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2070,27 +2066,27 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2117,22 +2113,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2155,27 +2151,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2185,12 +2181,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2202,12 +2198,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2240,27 +2236,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2287,12 +2283,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2325,27 +2321,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2372,17 +2368,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2410,27 +2406,27 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2440,12 +2436,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2457,22 +2453,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2491,31 +2487,31 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2525,7 +2521,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2542,17 +2538,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2576,26 +2572,26 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2610,12 +2606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -2627,12 +2623,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2665,22 +2661,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2712,17 +2708,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2750,27 +2746,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2780,12 +2776,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2797,22 +2793,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2835,22 +2831,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2865,14 +2861,10 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2882,22 +2874,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2920,27 +2912,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2950,12 +2942,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2967,22 +2959,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3005,22 +2997,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3035,12 +3027,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3052,22 +3044,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3090,22 +3082,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3120,12 +3112,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3137,22 +3129,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3175,27 +3167,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3205,7 +3197,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3222,22 +3214,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3260,27 +3252,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3290,7 +3282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -3307,22 +3299,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3341,31 +3333,31 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3375,12 +3367,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3392,22 +3384,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3430,27 +3422,27 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3460,12 +3452,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -3477,22 +3469,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3515,27 +3507,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3545,12 +3537,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3562,22 +3554,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3600,27 +3592,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3630,12 +3622,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3647,22 +3639,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3685,27 +3677,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3715,12 +3707,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3732,17 +3724,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3766,31 +3758,31 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3800,12 +3792,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3817,22 +3809,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3855,22 +3847,22 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3885,12 +3877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -3902,22 +3894,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3940,27 +3932,27 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3970,12 +3962,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -3987,17 +3979,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4025,27 +4017,27 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4072,12 +4064,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4110,27 +4102,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4157,17 +4149,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4191,31 +4183,31 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4225,12 +4217,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4242,17 +4234,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4280,27 +4272,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4310,12 +4302,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4327,17 +4319,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4365,27 +4357,27 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4395,12 +4387,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4412,17 +4404,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4450,27 +4442,27 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4480,12 +4472,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -4497,17 +4489,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4535,27 +4527,27 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4565,12 +4557,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -4582,17 +4574,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4616,31 +4608,31 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4650,7 +4642,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4667,17 +4659,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4701,31 +4693,31 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4735,12 +4727,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -4752,22 +4744,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4790,22 +4782,22 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4820,10 +4812,14 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n"/>
+          <t>ATHLETIC BREWING CO</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>ATHLETIC BREWING COMPANY</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4833,17 +4829,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4871,22 +4867,22 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4901,12 +4897,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -4918,17 +4914,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4956,22 +4952,22 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4986,12 +4982,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -5003,22 +4999,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5041,22 +5037,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -5071,12 +5067,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -5088,22 +5084,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5126,22 +5122,22 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -5156,7 +5152,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -5173,22 +5169,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5211,22 +5207,22 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -5241,12 +5237,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5258,17 +5254,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -5296,22 +5292,22 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -5326,12 +5322,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -5343,17 +5339,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5381,27 +5377,27 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5411,12 +5407,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5428,22 +5424,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5462,31 +5458,31 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5496,12 +5492,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -5513,22 +5509,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5551,27 +5547,27 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5581,12 +5577,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5598,22 +5594,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5636,27 +5632,27 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5666,12 +5662,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -5683,22 +5679,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5721,27 +5717,27 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5751,12 +5747,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5768,22 +5764,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5806,27 +5802,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5836,12 +5832,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5853,22 +5849,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5891,27 +5887,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5921,12 +5917,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5938,22 +5934,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5972,31 +5968,31 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -6006,12 +6002,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -6023,22 +6019,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6061,22 +6057,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -6091,14 +6087,10 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n"/>
       <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -6108,22 +6100,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6146,22 +6138,22 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -6176,12 +6168,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6193,22 +6185,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6231,22 +6223,22 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6261,12 +6253,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6278,22 +6270,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -6316,22 +6308,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -6346,12 +6338,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -6363,22 +6355,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6401,22 +6393,22 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -6431,12 +6423,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6448,22 +6440,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -6486,22 +6478,22 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -6516,12 +6508,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6533,83 +6525,1358 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>09/08/2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>THE LIQUOR SHOP</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>21033</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>498 E 30TH STREET</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ORO</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>09/08/2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Derrick laws</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>THE LIQUOR SHOP</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>21033</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>498 E 30TH STREET</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>TRULY HARD SELTZER</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>81006</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>21-00 MAPLE AVE</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="n">
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q72" s="3" t="inlineStr">
+      <c r="Q87" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -6688,6 +7955,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -629,27 +629,27 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -710,26 +710,26 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -795,31 +795,31 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -880,31 +880,31 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -965,31 +965,31 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -999,10 +999,14 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1012,7 +1016,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1022,7 +1026,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1046,31 +1050,31 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1080,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1097,7 +1101,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1107,7 +1111,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1131,31 +1135,31 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1182,17 +1186,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1216,31 +1220,31 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1267,12 +1271,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1301,26 +1305,26 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1335,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1352,17 +1356,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1386,31 +1390,31 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1420,14 +1424,10 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1437,17 +1437,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1471,31 +1471,31 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1522,22 +1522,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1556,31 +1556,31 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1641,26 +1641,26 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1692,12 +1692,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1726,26 +1726,26 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1845,10 +1845,14 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n"/>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1858,22 +1862,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1892,31 +1896,31 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1926,14 +1930,10 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1943,22 +1943,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1977,31 +1977,31 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2028,22 +2028,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2062,31 +2062,31 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2147,31 +2147,31 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2198,22 +2198,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2232,31 +2232,31 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -2283,22 +2283,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -2368,22 +2368,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2402,31 +2402,31 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2453,22 +2453,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2487,31 +2487,31 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2538,22 +2538,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2572,31 +2572,31 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2623,22 +2623,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2657,31 +2657,31 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2708,22 +2708,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2746,27 +2746,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2776,14 +2776,10 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n"/>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2793,22 +2789,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2831,27 +2827,27 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2861,10 +2857,14 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2874,12 +2874,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2959,22 +2959,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2997,27 +2997,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3082,22 +3082,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3167,22 +3167,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3214,12 +3214,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3252,22 +3252,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3299,17 +3299,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3384,17 +3384,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3469,17 +3469,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3503,31 +3503,31 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3554,12 +3554,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3592,27 +3592,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3639,17 +3639,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3677,27 +3677,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3724,22 +3724,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3758,31 +3758,31 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3792,14 +3792,10 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3809,17 +3805,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3847,27 +3843,27 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3894,22 +3890,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3932,27 +3928,27 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3962,7 +3958,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -3979,22 +3975,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4017,27 +4013,27 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4047,12 +4043,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4064,17 +4060,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4102,27 +4098,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4149,22 +4145,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4187,27 +4183,27 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4217,12 +4213,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4234,22 +4230,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4272,27 +4268,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4302,12 +4298,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4319,22 +4315,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4357,27 +4353,27 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4387,12 +4383,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4404,22 +4400,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4442,27 +4438,27 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4472,7 +4468,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -4489,22 +4485,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4527,27 +4523,27 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4557,7 +4553,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4574,22 +4570,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4608,31 +4604,31 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4642,12 +4638,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -4659,17 +4655,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4693,31 +4689,31 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4727,12 +4723,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -4744,22 +4740,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4782,22 +4778,22 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4812,12 +4808,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -4829,22 +4825,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4867,27 +4863,27 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4897,12 +4893,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -4914,22 +4910,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4952,27 +4948,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4982,12 +4978,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -4999,22 +4995,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5037,22 +5033,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -5067,12 +5063,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -5084,17 +5080,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -5122,22 +5118,22 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -5152,12 +5148,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -5169,17 +5165,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5207,22 +5203,22 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -5237,12 +5233,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5254,22 +5250,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5292,22 +5288,22 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -5322,12 +5318,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -5339,22 +5335,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5377,27 +5373,27 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5407,7 +5403,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -5424,17 +5420,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5458,31 +5454,31 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5492,12 +5488,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -5509,17 +5505,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5543,31 +5539,31 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5577,12 +5573,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5594,17 +5590,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5632,27 +5628,27 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5662,12 +5658,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -5679,17 +5675,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5717,27 +5713,27 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5747,12 +5743,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5764,17 +5760,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5802,27 +5798,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5832,12 +5828,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5849,17 +5845,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5887,27 +5883,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5917,12 +5913,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5934,17 +5930,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -5968,31 +5964,31 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -6002,12 +5998,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -6019,22 +6015,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6057,22 +6053,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -6087,10 +6083,14 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="n"/>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -6100,17 +6100,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6185,22 +6185,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6223,22 +6223,22 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -6270,17 +6270,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6308,27 +6308,27 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6389,31 +6389,31 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6440,22 +6440,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -6478,27 +6478,27 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6525,22 +6525,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6563,27 +6563,27 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6610,22 +6610,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6648,27 +6648,27 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -6695,22 +6695,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6733,27 +6733,27 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -6780,22 +6780,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6818,27 +6818,27 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -6865,22 +6865,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6899,31 +6899,31 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -6950,12 +6950,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6988,22 +6988,22 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -7018,14 +7018,10 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>CONSTELLATION BRANDS</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="n"/>
       <c r="Q77" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7035,22 +7031,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7073,22 +7069,22 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -7103,12 +7099,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7120,22 +7116,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7158,22 +7154,22 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -7188,12 +7184,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -7205,22 +7201,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7243,22 +7239,22 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -7273,12 +7269,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7290,22 +7286,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7328,22 +7324,22 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -7358,12 +7354,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -7375,22 +7371,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7413,22 +7409,22 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -7443,12 +7439,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7460,22 +7456,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -7498,22 +7494,22 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -7528,7 +7524,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -7545,22 +7541,22 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7583,22 +7579,22 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -7630,12 +7626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7668,22 +7664,22 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7698,12 +7694,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -7715,12 +7711,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7753,22 +7749,22 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7783,12 +7779,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7800,83 +7796,1018 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q87" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>81006</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>21-00 MAPLE AVE</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="n">
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr">
+      <c r="P98" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q87" s="3" t="inlineStr">
+      <c r="Q98" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -7970,6 +8901,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8014,7 +8956,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/30/2026</t>
         </is>
       </c>
     </row>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -714,22 +714,22 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,22 +846,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -884,27 +884,27 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -969,22 +969,22 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1016,12 +1016,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,22 +1101,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1139,27 +1139,27 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1186,12 +1186,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1309,27 +1309,27 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,12 +1356,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1424,10 +1424,14 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1437,17 +1441,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1475,27 +1479,27 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1522,22 +1526,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1560,27 +1564,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1590,14 +1594,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1607,17 +1607,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1641,31 +1641,31 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1692,22 +1692,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1896,26 +1896,26 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1930,10 +1930,14 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="n"/>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1943,12 +1947,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1977,26 +1981,26 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2011,12 +2015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2028,12 +2032,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2062,26 +2066,26 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2096,14 +2100,10 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2113,12 +2113,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2147,26 +2147,26 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2453,12 +2453,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2776,10 +2776,14 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="n"/>
+          <t>TRULY HARD SELTZER</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2789,22 +2793,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2823,31 +2827,31 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2857,12 +2861,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2874,22 +2878,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2912,27 +2916,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2942,14 +2946,10 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n"/>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2959,12 +2959,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3044,22 +3044,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3082,27 +3082,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3167,17 +3167,17 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3214,22 +3214,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3252,27 +3252,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3299,17 +3299,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3384,17 +3384,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3503,21 +3503,21 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3554,17 +3554,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3592,27 +3592,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3673,26 +3673,26 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -3724,22 +3724,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3762,27 +3762,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3792,10 +3792,14 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3805,17 +3809,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3843,27 +3847,27 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3873,12 +3877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -3890,12 +3894,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3928,17 +3932,17 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3958,14 +3962,10 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3975,22 +3975,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4013,27 +4013,27 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4060,22 +4060,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4098,27 +4098,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4145,22 +4145,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4183,27 +4183,27 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4230,12 +4230,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -4485,12 +4485,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4523,17 +4523,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4608,17 +4608,17 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4655,22 +4655,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4689,31 +4689,31 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -4740,17 +4740,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4778,27 +4778,27 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4825,22 +4825,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4859,31 +4859,31 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -4910,17 +4910,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4948,27 +4948,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -5033,27 +5033,27 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5118,27 +5118,27 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -5165,22 +5165,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5203,22 +5203,22 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5403,12 +5403,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5420,12 +5420,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -5505,17 +5505,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5539,26 +5539,26 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5590,17 +5590,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5628,22 +5628,22 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5709,26 +5709,26 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5798,22 +5798,22 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5845,12 +5845,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5883,22 +5883,22 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6185,22 +6185,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6223,22 +6223,22 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6270,22 +6270,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -6308,27 +6308,27 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6389,31 +6389,31 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6440,22 +6440,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
@@ -6593,12 +6593,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -6950,22 +6950,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6988,27 +6988,27 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7018,10 +7018,14 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="n"/>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7031,17 +7035,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7065,31 +7069,31 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7099,12 +7103,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7116,22 +7120,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7154,22 +7158,22 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -7184,14 +7188,10 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="n"/>
       <c r="Q79" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7201,22 +7201,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7286,22 +7286,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7324,22 +7324,22 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -7371,12 +7371,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -7409,17 +7409,17 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7456,12 +7456,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -7626,22 +7626,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7664,22 +7664,22 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -7711,22 +7711,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7749,22 +7749,22 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7796,12 +7796,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -7966,12 +7966,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -8051,12 +8051,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8136,12 +8136,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -8221,22 +8221,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8259,22 +8259,22 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -8344,22 +8344,22 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8391,22 +8391,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8429,22 +8429,22 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -8459,12 +8459,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8476,12 +8476,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8561,12 +8561,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -8646,12 +8646,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:29 AM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -8731,83 +8731,253 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="n">
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
+      <c r="P100" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q98" s="3" t="inlineStr">
+      <c r="Q100" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -8912,6 +9082,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -629,27 +629,27 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -714,22 +714,22 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -799,22 +799,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -846,22 +846,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1016,17 +1016,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,22 +1101,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1139,27 +1139,27 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1186,22 +1186,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1224,27 +1224,27 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1271,12 +1271,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,12 +1356,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1441,17 +1441,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1479,27 +1479,27 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1526,17 +1526,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1564,27 +1564,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1594,10 +1594,14 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1607,12 +1611,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1675,14 +1679,10 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1692,22 +1692,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1730,27 +1730,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1777,22 +1777,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2066,26 +2066,26 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2100,10 +2100,14 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n"/>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2113,12 +2117,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2147,26 +2151,26 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2181,14 +2185,10 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n"/>
       <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2198,12 +2198,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2232,26 +2232,26 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2453,12 +2453,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2793,12 +2793,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2912,21 +2912,21 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2946,10 +2946,14 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n"/>
+          <t>TWISTED TEA ORIGINAL</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2959,22 +2963,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2997,27 +3001,27 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3027,14 +3031,10 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3044,12 +3044,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3082,17 +3082,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3167,17 +3167,17 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3214,22 +3214,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3252,27 +3252,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3299,22 +3299,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3469,17 +3469,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3554,12 +3554,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3724,17 +3724,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3758,31 +3758,31 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3809,17 +3809,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3847,27 +3847,27 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -3894,22 +3894,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3962,10 +3962,14 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="n"/>
+          <t>TWISTED TEA ORIGINAL</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3975,22 +3979,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4013,27 +4017,27 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4043,14 +4047,10 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n"/>
       <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4060,22 +4060,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4098,27 +4098,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4230,22 +4230,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4268,27 +4268,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4315,12 +4315,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4485,12 +4485,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4523,17 +4523,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4608,17 +4608,17 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4693,17 +4693,17 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4825,22 +4825,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4859,31 +4859,31 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -4910,22 +4910,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4944,31 +4944,31 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -5033,27 +5033,27 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5118,27 +5118,27 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5203,27 +5203,27 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5288,22 +5288,22 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -5675,17 +5675,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5709,26 +5709,26 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5760,7 +5760,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -5794,26 +5794,26 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5845,12 +5845,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5883,17 +5883,17 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5930,12 +5930,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5968,22 +5968,22 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -6308,22 +6308,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6393,22 +6393,22 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6440,12 +6440,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -6478,27 +6478,27 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6525,22 +6525,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6559,26 +6559,26 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -6678,12 +6678,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7120,22 +7120,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7154,31 +7154,31 @@
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -7188,10 +7188,14 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="n"/>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7201,22 +7205,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7239,22 +7243,22 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -7269,14 +7273,10 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="n"/>
       <c r="Q80" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -7371,22 +7371,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7409,22 +7409,22 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7494,17 +7494,17 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -7541,12 +7541,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -7626,12 +7626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -7711,12 +7711,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -7796,22 +7796,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7834,22 +7834,22 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -7966,12 +7966,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -8051,12 +8051,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -8221,12 +8221,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8391,22 +8391,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8429,22 +8429,22 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -8476,22 +8476,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -8514,22 +8514,22 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8561,12 +8561,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -8646,12 +8646,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:29 AM</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -8901,83 +8901,168 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="n">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
+      <c r="P101" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q100" s="3" t="inlineStr">
+      <c r="Q101" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -9084,6 +9169,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 09:46 AM</t>
+          <t>09/30/2026 02:30 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>SAM'S LIQ WINE (P)</t>
+          <t>BOONTON LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>325 W CLINTON ST</t>
+          <t>119 HAWKINS PL</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>DOVER</t>
+          <t>BOONTON</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -676,22 +676,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>09/30/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>MAIN STREET LIQUOR</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>340 S MAIN ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -761,22 +761,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>09/30/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -799,27 +799,27 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>SAVERS CLUB LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>314 CLIFTON AVE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,22 +846,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/30/2026 10:39 AM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -884,27 +884,27 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -914,14 +914,10 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -931,22 +927,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/30/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -956,7 +952,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -969,27 +965,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1016,22 +1012,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1054,22 +1050,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1084,12 +1080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,17 +1097,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1139,27 +1135,27 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1186,22 +1182,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1224,27 +1220,27 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1271,17 +1267,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1309,27 +1305,27 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1339,12 +1335,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1356,22 +1352,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1394,27 +1390,27 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1424,12 +1420,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1441,17 +1437,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1479,27 +1475,27 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1509,12 +1505,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1526,17 +1522,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1564,27 +1560,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1611,22 +1607,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1649,27 +1645,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1679,10 +1675,14 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1692,12 +1692,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1777,22 +1777,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1862,17 +1862,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1896,31 +1896,31 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1981,26 +1981,26 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2032,17 +2032,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2066,31 +2066,31 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2100,14 +2100,10 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2117,17 +2113,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2151,31 +2147,31 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2185,10 +2181,14 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2198,22 +2198,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2232,31 +2232,31 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2317,26 +2317,26 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2402,26 +2402,26 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2453,12 +2453,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2487,26 +2487,26 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2572,26 +2572,26 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2606,14 +2606,10 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2623,12 +2619,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2661,22 +2657,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2691,12 +2687,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2708,12 +2704,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2742,7 +2738,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -2776,7 +2772,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2793,12 +2789,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2827,7 +2823,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2861,12 +2857,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2878,12 +2874,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2963,12 +2959,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2997,21 +2993,21 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3031,10 +3027,14 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n"/>
+          <t>TRULY HARD SELTZER</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3044,22 +3044,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3078,31 +3078,31 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3129,22 +3129,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3163,31 +3163,31 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3214,22 +3214,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3252,27 +3252,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3299,17 +3299,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3333,31 +3333,31 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3384,22 +3384,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3452,14 +3452,10 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3469,12 +3465,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3507,17 +3503,17 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3554,17 +3550,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3592,27 +3588,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3622,12 +3618,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3639,17 +3635,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3677,27 +3673,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3724,22 +3720,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3758,26 +3754,26 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3792,12 +3788,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3809,12 +3805,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3847,17 +3843,17 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3894,17 +3890,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3932,27 +3928,27 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3962,12 +3958,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -3979,22 +3975,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4017,22 +4013,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4047,10 +4043,14 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="n"/>
+          <t>TWISTED TEA ORIGINAL</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4060,17 +4060,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4098,27 +4098,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4145,22 +4145,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4179,26 +4179,26 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4230,22 +4230,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4268,27 +4268,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4315,17 +4315,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4400,22 +4400,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4438,27 +4438,27 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4468,14 +4468,10 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n"/>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4485,12 +4481,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4523,22 +4519,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4570,22 +4566,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4608,27 +4604,27 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4638,7 +4634,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4655,22 +4651,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4693,27 +4689,27 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4723,12 +4719,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -4740,12 +4736,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4778,17 +4774,17 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4798,7 +4794,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4825,12 +4821,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4863,17 +4859,17 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4910,22 +4906,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4944,31 +4940,31 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4978,7 +4974,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -4995,17 +4991,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -5033,27 +5029,27 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5080,12 +5076,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5118,27 +5114,27 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5165,12 +5161,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5203,27 +5199,27 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5250,17 +5246,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -5288,27 +5284,27 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5335,17 +5331,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5369,31 +5365,31 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5403,12 +5399,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5420,22 +5416,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5458,22 +5454,22 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5488,12 +5484,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -5505,22 +5501,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5543,27 +5539,27 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5573,12 +5569,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5590,22 +5586,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5628,27 +5624,27 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5658,7 +5654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -5675,22 +5671,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5713,22 +5709,22 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5743,7 +5739,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -5760,7 +5756,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -5770,7 +5766,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5794,26 +5790,26 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5828,12 +5824,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5845,17 +5841,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5883,22 +5879,22 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5913,12 +5909,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5930,17 +5926,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -5968,22 +5964,22 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5998,12 +5994,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -6015,17 +6011,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6053,22 +6049,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -6083,12 +6079,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6100,17 +6096,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -6138,22 +6134,22 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -6168,12 +6164,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6185,12 +6181,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -6219,26 +6215,26 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6253,12 +6249,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6270,12 +6266,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -6308,22 +6304,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -6338,12 +6334,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -6355,12 +6351,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -6423,12 +6419,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6440,22 +6436,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -6478,22 +6474,22 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -6508,12 +6504,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6525,22 +6521,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6563,27 +6559,27 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -6593,12 +6589,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6610,17 +6606,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6644,31 +6640,31 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6678,12 +6674,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -6695,17 +6691,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6733,27 +6729,27 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6763,12 +6759,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -6780,17 +6776,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6818,27 +6814,27 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6848,12 +6844,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -6865,22 +6861,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6903,27 +6899,27 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6933,12 +6929,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -6950,22 +6946,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6988,22 +6984,22 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -7018,12 +7014,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -7040,7 +7036,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -7069,7 +7065,7 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
@@ -7103,12 +7099,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7125,7 +7121,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -7154,7 +7150,7 @@
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
@@ -7188,12 +7184,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -7205,22 +7201,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7243,27 +7239,27 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7273,10 +7269,14 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="n"/>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7286,17 +7286,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -7324,27 +7324,27 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -7371,17 +7371,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7409,27 +7409,27 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7456,22 +7456,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -7494,27 +7494,27 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -7541,22 +7541,22 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7575,31 +7575,31 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -7626,22 +7626,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7664,22 +7664,22 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7694,14 +7694,10 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
-        </is>
-      </c>
-      <c r="P85" s="2" t="inlineStr">
-        <is>
-          <t>VINAIO IMPORTS LTD</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="n"/>
       <c r="Q85" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7711,22 +7707,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7749,22 +7745,22 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7779,12 +7775,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7796,22 +7792,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7834,22 +7830,22 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7864,12 +7860,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7881,22 +7877,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7919,22 +7915,22 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7949,12 +7945,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -7966,22 +7962,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -8004,22 +8000,22 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -8034,12 +8030,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -8051,22 +8047,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8089,22 +8085,22 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -8119,12 +8115,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8136,22 +8132,22 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -8174,22 +8170,22 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -8204,7 +8200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -8221,22 +8217,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8259,22 +8255,22 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -8306,12 +8302,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -8374,12 +8370,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8391,12 +8387,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -8459,7 +8455,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -8476,22 +8472,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -8514,22 +8510,22 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -8544,12 +8540,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8561,12 +8557,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8599,22 +8595,22 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -8629,12 +8625,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -8646,12 +8642,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -8684,22 +8680,22 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -8714,7 +8710,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -8731,12 +8727,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -8769,22 +8765,22 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -8799,12 +8795,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -8816,12 +8812,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8854,22 +8850,22 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -8884,12 +8880,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -8901,22 +8897,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8939,22 +8935,22 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8969,12 +8965,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -8986,83 +8982,508 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q103" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q104" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q105" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="n">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr">
+      <c r="P106" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q101" s="3" t="inlineStr">
+      <c r="Q106" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -9170,6 +9591,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q106"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 02:30 PM</t>
+          <t>10/05/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BOONTON LIQUOR LOCKER</t>
+          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>190208</t>
+          <t>230427</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>119 HAWKINS PL</t>
+          <t>125 WATER ST</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>BOONTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:49 AM</t>
+          <t>10/05/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -714,22 +714,22 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MAIN STREET LIQUOR</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>190913</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>340 S MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -761,22 +761,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:02 AM</t>
+          <t>10/05/2026 10:15 AM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -799,22 +799,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>SAVERS CLUB LIQUOR LOCKER</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>314 CLIFTON AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -846,12 +846,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:39 AM</t>
+          <t>09/30/2026 02:30 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>BOONTON LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>119 HAWKINS PL</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>BOONTON</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -914,10 +914,14 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -927,12 +931,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:38 AM</t>
+          <t>09/30/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -965,17 +969,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>MAIN STREET LIQUOR</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>340 S MAIN ST</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1012,22 +1016,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 09:46 AM</t>
+          <t>09/30/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1050,22 +1054,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>SAM'S LIQ WINE (P)</t>
+          <t>SAVERS CLUB LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>325 W CLINTON ST</t>
+          <t>314 CLIFTON AVE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>DOVER</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1080,12 +1084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1097,22 +1101,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>09/30/2026 10:39 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1135,27 +1139,27 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1165,14 +1169,10 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1182,22 +1182,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>09/30/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1220,27 +1220,27 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1305,27 +1305,27 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1352,22 +1352,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1475,27 +1475,27 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1522,17 +1522,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1607,17 +1607,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1645,27 +1645,27 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1692,17 +1692,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1730,27 +1730,27 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1862,22 +1862,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1900,27 +1900,27 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1947,17 +1947,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1985,27 +1985,27 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2070,22 +2070,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2100,10 +2100,14 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n"/>
+          <t>FAMOSA LAGER</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2113,12 +2117,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2151,22 +2155,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2198,22 +2202,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2236,27 +2240,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2283,17 +2287,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2317,31 +2321,31 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2351,14 +2355,10 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2368,17 +2368,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2402,31 +2402,31 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -2453,22 +2453,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2572,26 +2572,26 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2606,10 +2606,14 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2619,12 +2623,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2653,26 +2657,26 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2687,12 +2691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2704,12 +2708,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2738,26 +2742,26 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2772,7 +2776,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2789,12 +2793,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2823,26 +2827,26 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2857,14 +2861,10 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n"/>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2874,12 +2874,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2912,22 +2912,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -3027,12 +3027,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3214,12 +3214,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -3299,12 +3299,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3452,10 +3452,14 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3465,22 +3469,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3503,27 +3507,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3533,12 +3537,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3550,22 +3554,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3584,31 +3588,31 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3618,12 +3622,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3635,22 +3639,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3673,27 +3677,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3703,14 +3707,10 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n"/>
       <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3720,22 +3720,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3758,27 +3758,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3805,12 +3805,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3843,17 +3843,17 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3928,17 +3928,17 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3975,22 +3975,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4013,22 +4013,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4060,17 +4060,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4098,27 +4098,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4145,17 +4145,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4179,31 +4179,31 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4230,17 +4230,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4268,27 +4268,27 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4315,12 +4315,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4353,22 +4353,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4400,22 +4400,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4434,26 +4434,26 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4468,10 +4468,14 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="n"/>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4481,12 +4485,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4519,17 +4523,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4539,7 +4543,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4566,22 +4570,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4604,22 +4608,22 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4634,12 +4638,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -4651,12 +4655,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4689,17 +4693,17 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4719,14 +4723,10 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n"/>
       <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4736,12 +4736,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4774,27 +4774,27 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4821,22 +4821,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4859,27 +4859,27 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -4906,22 +4906,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4944,27 +4944,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -4991,12 +4991,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5114,17 +5114,17 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5161,12 +5161,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5199,17 +5199,17 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5331,22 +5331,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5365,31 +5365,31 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -5416,17 +5416,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5454,27 +5454,27 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5501,12 +5501,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5539,22 +5539,22 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5586,22 +5586,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5620,31 +5620,31 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5709,22 +5709,22 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5756,22 +5756,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5794,27 +5794,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5879,27 +5879,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5926,22 +5926,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5964,22 +5964,22 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -6011,12 +6011,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6096,12 +6096,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6181,17 +6181,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -6215,26 +6215,26 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6266,17 +6266,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6304,22 +6304,22 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -6351,17 +6351,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -6419,12 +6419,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6436,12 +6436,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -6470,26 +6470,26 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6521,12 +6521,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6559,22 +6559,22 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6644,22 +6644,22 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6814,22 +6814,22 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -6861,22 +6861,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6899,22 +6899,22 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -6946,22 +6946,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6984,27 +6984,27 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -7031,17 +7031,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7065,31 +7065,31 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7099,12 +7099,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7116,22 +7116,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7154,27 +7154,27 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -7201,22 +7201,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -7626,22 +7626,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7664,27 +7664,27 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -7694,10 +7694,14 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P85" s="2" t="n"/>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7707,17 +7711,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -7745,27 +7749,27 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7792,17 +7796,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -7826,31 +7830,31 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7860,12 +7864,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7877,22 +7881,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7915,22 +7919,22 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7945,14 +7949,10 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
-        </is>
-      </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="n"/>
       <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7962,22 +7962,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -8000,22 +8000,22 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -8047,22 +8047,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8085,22 +8085,22 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8132,12 +8132,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -8170,17 +8170,17 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -8217,12 +8217,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -8302,22 +8302,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -8340,22 +8340,22 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8387,22 +8387,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8425,22 +8425,22 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8472,22 +8472,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -8510,22 +8510,22 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8557,12 +8557,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -8642,12 +8642,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -8727,12 +8727,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -8812,12 +8812,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -8897,22 +8897,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8935,22 +8935,22 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -8982,12 +8982,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
@@ -9067,12 +9067,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -9105,22 +9105,22 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q102" s="3" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -9190,22 +9190,22 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
@@ -9237,12 +9237,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q104" s="3" t="inlineStr">
@@ -9322,12 +9322,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q105" s="3" t="inlineStr">
@@ -9407,83 +9407,338 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q106" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q107" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q108" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="n">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P106" s="2" t="inlineStr">
+      <c r="P109" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q106" s="3" t="inlineStr">
+      <c r="Q109" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -9596,6 +9851,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9640,7 +9898,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
     </row>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Filters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 11:37 AM</t>
+          <t>10/08/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>230427</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>125 WATER ST</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MONACO LIME CRUSH</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:59 AM</t>
+          <t>10/08/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -710,26 +710,26 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>COBBLESTONE HILL DELI</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>287 BROAD ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,14 +744,10 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -761,22 +757,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:15 AM</t>
+          <t>10/07/2026 02:08 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -795,26 +791,26 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>10 NJ-17</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>RUTHERFORD</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -829,14 +825,10 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -846,17 +838,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 02:30 PM</t>
+          <t>10/07/2026 11:12 AM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -884,22 +876,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>BOONTON LIQUOR LOCKER</t>
+          <t>LIQUOR FACTORY III SPARTA</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>190208</t>
+          <t>230114</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119 HAWKINS PL</t>
+          <t>41 WOODPORT ROAD</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>BOONTON</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -931,17 +923,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:49 AM</t>
+          <t>10/07/2026 10:14 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -969,22 +961,22 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>MAIN STREET LIQUOR</t>
+          <t>SUPER SAVER LIQ</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>190913</t>
+          <t>191408</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>340 S MAIN ST</t>
+          <t>322 HOWARD BLVD</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>MT ARLINGTON</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1016,22 +1008,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:02 AM</t>
+          <t>10/06/2026 03:33 PM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1054,22 +1046,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>SAVERS CLUB LIQUOR LOCKER</t>
+          <t>GARDEN LIQUORS (P)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>314 CLIFTON AVE</t>
+          <t>300 HARRISON AVE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1084,12 +1076,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1101,22 +1093,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:39 AM</t>
+          <t>10/06/2026 02:35 PM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1139,22 +1131,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1169,10 +1161,14 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1182,22 +1178,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:38 AM</t>
+          <t>10/06/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1220,22 +1216,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1267,22 +1263,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 09:46 AM</t>
+          <t>10/06/2026 02:02 PM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1305,22 +1301,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>SAM'S LIQ WINE (P)</t>
+          <t>SHOP RITE LIQ.(A)LODI</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>325 W CLINTON ST</t>
+          <t>150 MAIN STR</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>DOVER</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1330,7 +1326,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Cooler Door Wrap</t>
+          <t>POS, Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1352,22 +1348,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>10/06/2026 11:40 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1386,31 +1382,31 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>M &amp; M WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>429 MARKET ST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1420,14 +1416,10 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n"/>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1437,22 +1429,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>10/06/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1471,31 +1463,31 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>ALL STAR WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>77022</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>21 MIDLAND AVE</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1505,14 +1497,10 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1522,22 +1510,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>10/06/2026 09:37 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1556,31 +1544,31 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>FOOD MART LIQUOR</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>77001</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>430 MARKET ST</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1590,14 +1578,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1607,17 +1591,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>10/06/2026 09:24 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1632,7 +1616,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1641,31 +1625,31 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>545 BOULEVARD</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1675,14 +1659,10 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>CONSTELLATION BRANDS</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1692,22 +1672,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>10/05/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1730,22 +1710,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>230427</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>125 WATER ST</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1760,12 +1740,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -1777,22 +1757,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>10/05/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1815,27 +1795,27 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1862,7 +1842,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>10/05/2026 10:15 AM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1872,12 +1852,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1900,22 +1880,22 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1947,22 +1927,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/30/2026 02:30 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,27 +1965,27 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>BOONTON LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>119 HAWKINS PL</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>BOONTON</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2015,12 +1995,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2032,22 +2012,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/30/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2070,27 +2050,27 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>MAIN STREET LIQUOR</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>340 S MAIN ST</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2100,12 +2080,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2117,22 +2097,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/30/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2155,27 +2135,27 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>SAVERS CLUB LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>314 CLIFTON AVE</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2185,12 +2165,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2202,22 +2182,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/30/2026 10:39 AM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2240,27 +2220,27 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2270,14 +2250,10 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2287,22 +2263,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/30/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2325,27 +2301,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2355,10 +2331,14 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2368,22 +2348,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2406,27 +2386,27 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2453,7 +2433,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2463,12 +2443,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2491,27 +2471,27 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2538,7 +2518,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2572,7 +2552,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -2606,7 +2586,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2623,12 +2603,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2657,26 +2637,26 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2691,12 +2671,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -2708,22 +2688,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2733,7 +2713,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2742,26 +2722,26 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2776,12 +2756,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2793,17 +2773,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2827,31 +2807,31 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2861,10 +2841,14 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="n"/>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2874,17 +2858,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2908,31 +2892,31 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2942,12 +2926,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2959,22 +2943,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2993,31 +2977,31 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3027,7 +3011,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3044,17 +3028,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3078,31 +3062,31 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3112,12 +3096,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3129,17 +3113,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3163,31 +3147,31 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3197,12 +3181,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3214,7 +3198,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -3224,7 +3208,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3248,31 +3232,31 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3282,12 +3266,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3299,7 +3283,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -3333,26 +3317,26 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3367,12 +3351,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3384,7 +3368,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3394,7 +3378,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3418,31 +3402,31 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3452,14 +3436,10 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3469,7 +3449,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3479,7 +3459,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3507,27 +3487,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3537,12 +3517,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -3554,22 +3534,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3588,31 +3568,31 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3622,12 +3602,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3639,12 +3619,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3673,26 +3653,26 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3707,10 +3687,14 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3720,22 +3704,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3754,21 +3738,21 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3778,7 +3762,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3788,12 +3772,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3805,22 +3789,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3839,21 +3823,21 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3863,7 +3847,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3873,7 +3857,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -3890,22 +3874,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3924,31 +3908,31 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3958,14 +3942,10 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3975,17 +3955,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4009,31 +3989,31 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4043,12 +4023,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4060,22 +4040,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4094,31 +4074,31 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4128,7 +4108,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4145,22 +4125,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4179,31 +4159,31 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4213,7 +4193,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4230,22 +4210,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4264,31 +4244,31 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4315,7 +4295,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4325,12 +4305,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4349,31 +4329,31 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4383,12 +4363,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4400,7 +4380,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4410,12 +4390,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4434,31 +4414,31 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4468,12 +4448,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -4485,7 +4465,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4495,12 +4475,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4519,31 +4499,31 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4553,7 +4533,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4570,7 +4550,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -4580,12 +4560,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4608,27 +4588,27 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4638,7 +4618,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4655,7 +4635,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4665,7 +4645,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4689,31 +4669,31 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4723,10 +4703,14 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="n"/>
+          <t>TWISTED TEA ORIGINAL</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4736,7 +4720,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4746,12 +4730,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4774,27 +4758,27 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4804,14 +4788,10 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n"/>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4821,22 +4801,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4859,27 +4839,27 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4889,7 +4869,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -4906,22 +4886,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4944,27 +4924,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4974,12 +4954,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -4991,12 +4971,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -5029,22 +5009,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -5076,22 +5056,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5114,27 +5094,27 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5144,12 +5124,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -5161,12 +5141,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5199,27 +5179,27 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5246,12 +5226,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5284,27 +5264,27 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5331,17 +5311,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5369,27 +5349,27 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5399,12 +5379,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5416,17 +5396,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5454,27 +5434,27 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5501,17 +5481,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5535,31 +5515,31 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5569,12 +5549,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5586,22 +5566,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5620,31 +5600,31 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5654,7 +5634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -5671,17 +5651,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5709,22 +5689,22 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5739,12 +5719,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5756,22 +5736,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5794,27 +5774,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5824,14 +5804,10 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n"/>
       <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5841,12 +5817,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5879,17 +5855,17 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5899,7 +5875,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5926,22 +5902,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5964,22 +5940,22 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5994,7 +5970,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -6011,22 +5987,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6049,22 +6025,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -6079,12 +6055,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6096,22 +6072,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6134,27 +6110,27 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -6164,12 +6140,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -6181,22 +6157,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6219,27 +6195,27 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -6249,12 +6225,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6266,22 +6242,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -6304,27 +6280,27 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6334,7 +6310,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -6351,22 +6327,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6389,27 +6365,27 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6419,7 +6395,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -6436,22 +6412,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -6470,31 +6446,31 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6504,12 +6480,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6521,22 +6497,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6559,27 +6535,27 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -6589,12 +6565,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6606,22 +6582,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6644,27 +6620,27 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6674,12 +6650,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -6691,17 +6667,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6725,31 +6701,31 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6759,12 +6735,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -6776,22 +6752,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6814,22 +6790,22 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6844,12 +6820,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -6861,22 +6837,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6899,27 +6875,27 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6929,12 +6905,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -6946,22 +6922,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6984,27 +6960,27 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7014,12 +6990,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -7031,22 +7007,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7069,22 +7045,22 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -7099,12 +7075,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7116,22 +7092,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7154,22 +7130,22 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -7184,12 +7160,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -7201,22 +7177,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7239,27 +7215,27 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7269,12 +7245,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7286,17 +7262,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -7320,31 +7296,31 @@
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -7354,12 +7330,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -7371,17 +7347,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7409,27 +7385,27 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -7439,12 +7415,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7456,17 +7432,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -7494,27 +7470,27 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -7524,12 +7500,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -7541,17 +7517,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7575,31 +7551,31 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -7609,7 +7585,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -7626,17 +7602,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -7664,27 +7640,27 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -7694,12 +7670,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -7711,17 +7687,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -7749,27 +7725,27 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7779,12 +7755,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7796,17 +7772,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -7830,31 +7806,31 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7864,12 +7840,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7881,22 +7857,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7919,22 +7895,22 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7949,10 +7925,14 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P88" s="2" t="n"/>
+          <t>CORONA LIGHT</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -7962,17 +7942,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -8000,22 +7980,22 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -8030,12 +8010,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -8047,17 +8027,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -8085,22 +8065,22 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -8115,12 +8095,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8132,7 +8112,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -8142,12 +8122,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -8170,22 +8150,22 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -8200,12 +8180,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -8217,7 +8197,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -8227,7 +8207,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -8255,22 +8235,22 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -8285,12 +8265,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8302,17 +8282,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -8340,27 +8320,27 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -8370,12 +8350,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8387,22 +8367,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8421,31 +8401,31 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -8455,12 +8435,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8472,22 +8452,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -8510,27 +8490,27 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -8540,12 +8520,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8557,22 +8537,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -8595,27 +8575,27 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -8625,12 +8605,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -8642,22 +8622,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -8680,27 +8660,27 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -8710,7 +8690,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -8727,22 +8707,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -8765,27 +8745,27 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -8795,12 +8775,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -8812,22 +8792,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -8850,27 +8830,27 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -8880,12 +8860,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -8897,22 +8877,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8931,31 +8911,31 @@
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8965,12 +8945,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -8982,12 +8962,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -9020,22 +9000,22 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -9050,14 +9030,10 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
-        </is>
-      </c>
-      <c r="P101" s="2" t="inlineStr">
-        <is>
-          <t>CAPE MAY BREWING COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="n"/>
       <c r="Q101" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -9067,22 +9043,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9105,22 +9081,22 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -9152,12 +9128,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -9190,22 +9166,22 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -9220,12 +9196,12 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
@@ -9237,22 +9213,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9275,22 +9251,22 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -9305,12 +9281,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q104" s="3" t="inlineStr">
@@ -9322,22 +9298,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -9360,22 +9336,22 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -9390,7 +9366,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -9407,22 +9383,22 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -9445,22 +9421,22 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -9475,12 +9451,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q106" s="3" t="inlineStr">
@@ -9492,22 +9468,22 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -9530,22 +9506,22 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -9560,12 +9536,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q107" s="3" t="inlineStr">
@@ -9577,22 +9553,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -9615,22 +9591,22 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -9645,12 +9621,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q108" s="3" t="inlineStr">
@@ -9662,83 +9638,1188 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 11:34 AM</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q109" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>TRULY HARD SELTZER</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q110" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q111" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q112" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q113" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="Q114" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q115" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>81006</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>21-00 MAPLE AVE</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q119" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q120" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q121" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="n">
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K122" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="L122" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="M122" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
+      <c r="P122" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q109" s="3" t="inlineStr">
+      <c r="Q122" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -9854,6 +10935,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9898,7 +10992,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>10/31/2026</t>
         </is>
       </c>
     </row>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q122"/>
+  <dimension ref="A1:Q124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 12:15 PM</t>
+          <t>10/12/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -659,14 +659,10 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>MONACO LIME CRUSH</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -676,7 +672,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 11:49 AM</t>
+          <t>10/12/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -686,12 +682,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -710,26 +706,26 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>COBBLESTONE HILL DELI</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>287 BROAD ST</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,10 +740,14 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n"/>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -757,17 +757,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 02:08 PM</t>
+          <t>10/08/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -791,26 +791,26 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10 NJ-17</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>RUTHERFORD</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -825,10 +825,14 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n"/>
+          <t>MONACO LIME CRUSH</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -838,22 +842,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 11:12 AM</t>
+          <t>10/08/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -872,26 +876,26 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR FACTORY III SPARTA</t>
+          <t>COBBLESTONE HILL DELI</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>230114</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41 WOODPORT ROAD</t>
+          <t>287 BROAD ST</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -906,14 +910,10 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -923,22 +923,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 10:14 AM</t>
+          <t>10/07/2026 02:08 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -957,26 +957,26 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>SUPER SAVER LIQ</t>
+          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>191408</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>322 HOWARD BLVD</t>
+          <t>10 NJ-17</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>MT ARLINGTON</t>
+          <t>RUTHERFORD</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -991,14 +991,10 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1008,22 +1004,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 03:33 PM</t>
+          <t>10/07/2026 11:12 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1046,22 +1042,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>GARDEN LIQUORS (P)</t>
+          <t>LIQUOR FACTORY III SPARTA</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>230114</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>300 HARRISON AVE</t>
+          <t>41 WOODPORT ROAD</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1093,22 +1089,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:35 PM</t>
+          <t>10/07/2026 10:14 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1131,22 +1127,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE DISCOUNT LIQUOR</t>
+          <t>SUPER SAVER LIQ</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>191408</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>183 ROUTE 46 WEST</t>
+          <t>322 HOWARD BLVD</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MT ARLINGTON</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1161,7 +1157,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1178,12 +1174,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:34 PM</t>
+          <t>10/06/2026 03:33 PM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1216,17 +1212,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE DISCOUNT LIQUOR</t>
+          <t>GARDEN LIQUORS (P)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>183 ROUTE 46 WEST</t>
+          <t>300 HARRISON AVE</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1246,7 +1242,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1263,12 +1259,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:02 PM</t>
+          <t>10/06/2026 02:35 PM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1301,17 +1297,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ.(A)LODI</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>150 MAIN STR</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1326,12 +1322,12 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>POS, Cooler Door Wrap</t>
+          <t>Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1348,22 +1344,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 11:40 AM</t>
+          <t>10/06/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1382,26 +1378,26 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>M &amp; M WINE &amp; SPIRITS</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>429 MARKET ST</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1416,10 +1412,14 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1429,22 +1429,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 11:02 AM</t>
+          <t>10/06/2026 02:02 PM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1463,26 +1463,26 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>ALL STAR WINE &amp; LIQUOR</t>
+          <t>SHOP RITE LIQ.(A)LODI</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77022</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21 MIDLAND AVE</t>
+          <t>150 MAIN STR</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1492,15 +1492,19 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Cooler Door Wrap</t>
+          <t>POS, Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1510,12 +1514,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:37 AM</t>
+          <t>10/06/2026 11:40 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1544,21 +1548,21 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>FOOD MART LIQUOR</t>
+          <t>M &amp; M WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77001</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>430 MARKET ST</t>
+          <t>429 MARKET ST</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1591,12 +1595,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:24 AM</t>
+          <t>10/06/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1625,21 +1629,21 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
+          <t>ALL STAR WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>77022</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>545 BOULEVARD</t>
+          <t>21 MIDLAND AVE</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1672,22 +1676,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 11:37 AM</t>
+          <t>10/06/2026 09:37 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1706,26 +1710,26 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
+          <t>FOOD MART LIQUOR</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>230427</t>
+          <t>77001</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125 WATER ST</t>
+          <t>430 MARKET ST</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1740,14 +1744,10 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1757,22 +1757,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:59 AM</t>
+          <t>10/06/2026 09:24 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1791,26 +1791,26 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>545 BOULEVARD</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1825,14 +1825,10 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1842,12 +1838,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:15 AM</t>
+          <t>10/05/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1880,22 +1876,22 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>230427</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>125 WATER ST</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1927,17 +1923,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 02:30 PM</t>
+          <t>10/05/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1965,22 +1961,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>BOONTON LIQUOR LOCKER</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>190208</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119 HAWKINS PL</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>BOONTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2012,17 +2008,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:49 AM</t>
+          <t>10/05/2026 10:15 AM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2050,22 +2046,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAIN STREET LIQUOR</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>190913</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>340 S MAIN ST</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2097,22 +2093,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:02 AM</t>
+          <t>09/30/2026 02:30 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2135,22 +2131,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>SAVERS CLUB LIQUOR LOCKER</t>
+          <t>BOONTON LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>314 CLIFTON AVE</t>
+          <t>119 HAWKINS PL</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>BOONTON</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2165,12 +2161,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2182,12 +2178,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:39 AM</t>
+          <t>09/30/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2220,17 +2216,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>MAIN STREET LIQUOR</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>340 S MAIN ST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2250,10 +2246,14 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2263,22 +2263,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:38 AM</t>
+          <t>09/30/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2301,22 +2301,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>SAVERS CLUB LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>314 CLIFTON AVE</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -2348,12 +2348,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 09:46 AM</t>
+          <t>09/30/2026 10:39 AM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>SAM'S LIQ WINE (P)</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>325 W CLINTON ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>DOVER</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2416,14 +2416,10 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2433,22 +2429,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>09/30/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2471,27 +2467,27 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2518,22 +2514,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2556,27 +2552,27 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2603,7 +2599,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2641,22 +2637,22 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2688,7 +2684,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2698,12 +2694,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2713,7 +2709,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2726,22 +2722,22 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2756,12 +2752,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -2773,17 +2769,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2811,17 +2807,17 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2831,7 +2827,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2841,12 +2837,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -2858,22 +2854,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2883,7 +2879,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2896,27 +2892,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2926,12 +2922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2943,22 +2939,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2981,22 +2977,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3011,12 +3007,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3028,12 +3024,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3066,17 +3062,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3096,12 +3092,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -3113,22 +3109,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3151,27 +3147,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3181,12 +3177,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -3198,12 +3194,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3266,12 +3262,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3283,17 +3279,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3321,27 +3317,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3351,12 +3347,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3368,12 +3364,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3406,22 +3402,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3436,10 +3432,14 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3449,17 +3449,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3487,27 +3487,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3534,22 +3534,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3572,27 +3572,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3602,14 +3602,10 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3619,17 +3615,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3653,31 +3649,31 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3687,7 +3683,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -3704,22 +3700,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3738,21 +3734,21 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3762,7 +3758,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3772,12 +3768,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -3789,12 +3785,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3823,7 +3819,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -3857,7 +3853,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -3874,12 +3870,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3908,26 +3904,26 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3942,10 +3938,14 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="n"/>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3955,12 +3955,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3989,26 +3989,26 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4040,12 +4040,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4074,26 +4074,26 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -4108,14 +4108,10 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n"/>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4125,12 +4121,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4159,26 +4155,26 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -4193,12 +4189,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4215,7 +4211,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4244,7 +4240,7 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -4278,12 +4274,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -4295,12 +4291,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4329,7 +4325,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -4363,12 +4359,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4380,12 +4376,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4448,12 +4444,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -4465,12 +4461,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4533,12 +4529,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -4550,12 +4546,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4584,7 +4580,7 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -4618,12 +4614,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -4635,12 +4631,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4669,7 +4665,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -4703,12 +4699,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -4720,12 +4716,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4758,17 +4754,17 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4788,10 +4784,14 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n"/>
+          <t>TRULY HARD SELTZER</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4801,22 +4801,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4835,31 +4835,31 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -4886,22 +4886,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4924,27 +4924,27 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4954,14 +4954,10 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n"/>
       <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4971,12 +4967,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -5009,17 +5005,17 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5056,22 +5052,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5094,27 +5090,27 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5124,12 +5120,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -5141,12 +5137,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5179,17 +5175,17 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5226,22 +5222,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5264,27 +5260,27 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5294,12 +5290,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -5311,17 +5307,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5349,27 +5345,27 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5379,12 +5375,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5396,17 +5392,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5434,27 +5430,27 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5481,12 +5477,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5515,21 +5511,21 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5549,7 +5545,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -5566,17 +5562,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5604,27 +5600,27 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5651,12 +5647,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5685,26 +5681,26 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5719,7 +5715,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -5736,22 +5732,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5774,27 +5770,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5804,10 +5800,14 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5817,17 +5817,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5855,27 +5855,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5902,12 +5902,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -5970,14 +5970,10 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n"/>
       <c r="Q65" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5987,22 +5983,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6025,27 +6021,27 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -6055,12 +6051,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6072,22 +6068,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6110,27 +6106,27 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -6140,7 +6136,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -6157,22 +6153,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6195,27 +6191,27 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -6225,12 +6221,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6242,12 +6238,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -6280,17 +6276,17 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -6300,7 +6296,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6327,12 +6323,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -6365,17 +6361,17 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6385,7 +6381,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6412,12 +6408,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -6450,17 +6446,17 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -6497,12 +6493,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6535,17 +6531,17 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6582,12 +6578,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6620,17 +6616,17 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -6640,7 +6636,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6667,22 +6663,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6701,31 +6697,31 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6735,7 +6731,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -6752,17 +6748,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6790,27 +6786,27 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6837,22 +6833,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6871,31 +6867,31 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6905,7 +6901,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -6922,17 +6918,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6960,27 +6956,27 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7007,17 +7003,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7045,27 +7041,27 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7092,7 +7088,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -7102,12 +7098,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7130,27 +7126,27 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -7160,12 +7156,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -7177,22 +7173,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7215,22 +7211,22 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -7245,12 +7241,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7267,7 +7263,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7330,7 +7326,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -7347,12 +7343,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -7415,12 +7411,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7432,12 +7428,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7500,12 +7496,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -7517,17 +7513,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7551,26 +7547,26 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -7585,12 +7581,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -7602,17 +7598,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -7640,22 +7636,22 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7670,12 +7666,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -7687,12 +7683,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7721,26 +7717,26 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7755,12 +7751,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7772,12 +7768,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7810,22 +7806,22 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7840,12 +7836,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7857,12 +7853,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7895,22 +7891,22 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7925,12 +7921,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -7947,7 +7943,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -8010,7 +8006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -8032,7 +8028,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -8095,7 +8091,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -8112,12 +8108,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -8150,22 +8146,22 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -8180,12 +8176,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -8197,22 +8193,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8235,22 +8231,22 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -8265,12 +8261,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8282,22 +8278,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -8320,27 +8316,27 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -8350,12 +8346,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8367,22 +8363,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8401,31 +8397,31 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -8435,12 +8431,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8452,22 +8448,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -8490,22 +8486,22 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -8520,12 +8516,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8542,7 +8538,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -8571,7 +8567,7 @@
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -8605,12 +8601,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -8627,7 +8623,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -8690,12 +8686,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -8712,7 +8708,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -8775,7 +8771,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -8797,7 +8793,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8860,7 +8856,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -8882,7 +8878,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8911,7 +8907,7 @@
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -8945,12 +8941,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -8962,22 +8958,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -9000,27 +8996,27 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -9030,10 +9026,14 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P101" s="2" t="n"/>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -9043,17 +9043,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -9077,31 +9077,31 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -9111,12 +9111,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q102" s="3" t="inlineStr">
@@ -9128,22 +9128,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -9166,22 +9166,22 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -9196,14 +9196,10 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
-        </is>
-      </c>
-      <c r="P103" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n"/>
       <c r="Q103" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -9213,22 +9209,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9251,22 +9247,22 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -9281,12 +9277,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q104" s="3" t="inlineStr">
@@ -9298,22 +9294,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -9336,22 +9332,22 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -9366,12 +9362,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q105" s="3" t="inlineStr">
@@ -9383,12 +9379,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -9421,17 +9417,17 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -9451,12 +9447,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q106" s="3" t="inlineStr">
@@ -9468,12 +9464,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -9536,7 +9532,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -9553,12 +9549,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -9621,12 +9617,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q108" s="3" t="inlineStr">
@@ -9638,22 +9634,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -9676,22 +9672,22 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -9706,12 +9702,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q109" s="3" t="inlineStr">
@@ -9723,22 +9719,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -9761,22 +9757,22 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -9791,12 +9787,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q110" s="3" t="inlineStr">
@@ -9808,12 +9804,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -9876,12 +9872,12 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
@@ -9893,12 +9889,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9961,12 +9957,12 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q112" s="3" t="inlineStr">
@@ -9978,12 +9974,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -10046,12 +10042,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q113" s="3" t="inlineStr">
@@ -10063,12 +10059,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -10131,12 +10127,12 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q114" s="3" t="inlineStr">
@@ -10148,12 +10144,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -10216,12 +10212,12 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q115" s="3" t="inlineStr">
@@ -10233,22 +10229,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/03/2026 11:30 AM</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10271,22 +10267,22 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -10301,12 +10297,12 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q116" s="3" t="inlineStr">
@@ -10318,12 +10314,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -10356,22 +10352,22 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -10386,12 +10382,12 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q117" s="3" t="inlineStr">
@@ -10403,22 +10399,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:11 AM</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -10441,22 +10437,22 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>21-00 MAPLE AVE</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -10471,12 +10467,12 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q118" s="3" t="inlineStr">
@@ -10488,12 +10484,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 10:31 AM</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -10556,12 +10552,12 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q119" s="3" t="inlineStr">
@@ -10573,12 +10569,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:30 AM</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -10641,12 +10637,12 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q120" s="3" t="inlineStr">
@@ -10658,12 +10654,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 10:29 AM</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -10726,12 +10722,12 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
@@ -10743,83 +10739,253 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q123" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="n">
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="M124" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N122" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr">
+      <c r="P124" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q122" s="3" t="inlineStr">
+      <c r="Q124" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -10948,6 +11114,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026 02:43 PM</t>
+          <t>10/15/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -625,26 +625,26 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026 02:43 PM</t>
+          <t>10/14/2026 01:34 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -706,31 +706,31 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>W E BEVERAGE (A)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>52019</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>91 W PALISADE AVE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -740,14 +740,10 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>DRINK CARBLISS</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -757,22 +753,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 12:15 PM</t>
+          <t>10/14/2026 01:34 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -795,22 +791,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>LINCOLN PARK FINE WINES &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>60 BEAVERBROOK ROAD</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>LINCOLN PARK</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -825,12 +821,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>MONACO LIME CRUSH</t>
+          <t>ATHLETIC RUN WILD NA IPA</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -842,17 +838,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 11:49 AM</t>
+          <t>10/14/2026 11:42 AM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -876,26 +872,26 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>COBBLESTONE HILL DELI</t>
+          <t>CARISMA LIQ &amp; GROC (P)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>287 BROAD ST</t>
+          <t>230 VREELAND AVE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -910,10 +906,14 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n"/>
+          <t>MONACO BLUE CRUSH</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -923,22 +923,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 02:08 PM</t>
+          <t>10/14/2026 11:28 AM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -957,26 +957,26 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10 NJ-17</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>RUTHERFORD</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -991,10 +991,14 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n"/>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1004,22 +1008,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 11:12 AM</t>
+          <t>10/14/2026 11:28 AM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1042,22 +1046,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR FACTORY III SPARTA</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>230114</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41 WOODPORT ROAD</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1089,22 +1093,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 10:14 AM</t>
+          <t>10/14/2026 11:28 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1127,22 +1131,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>SUPER SAVER LIQ</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>191408</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>322 HOWARD BLVD</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>MT ARLINGTON</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SIMPLY SPIKED VARIETY</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1174,22 +1178,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 03:33 PM</t>
+          <t>10/14/2026 07:25 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1212,22 +1216,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>GARDEN LIQUORS (P)</t>
+          <t>CORK &amp; KEG (A)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>75004</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>300 HARRISON AVE</t>
+          <t>89 KINDERKAMACK RD</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>EMERSON</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1242,12 +1246,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1259,12 +1263,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:35 PM</t>
+          <t>10/12/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1297,22 +1301,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE DISCOUNT LIQUOR</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>183 ROUTE 46 WEST</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1327,14 +1331,10 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1344,12 +1344,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:34 PM</t>
+          <t>10/12/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1382,22 +1382,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE DISCOUNT LIQUOR</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>183 ROUTE 46 WEST</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>CARBLISS</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>DRINK CARBLISS</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1429,22 +1429,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:02 PM</t>
+          <t>10/08/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1467,22 +1467,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ.(A)LODI</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150 MAIN STR</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>POS, Cooler Door Wrap</t>
+          <t>Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MONACO LIME CRUSH</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 11:40 AM</t>
+          <t>10/08/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1548,26 +1548,26 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>M &amp; M WINE &amp; SPIRITS</t>
+          <t>COBBLESTONE HILL DELI</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>429 MARKET ST</t>
+          <t>287 BROAD ST</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 11:02 AM</t>
+          <t>10/07/2026 02:08 PM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1629,26 +1629,26 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>ALL STAR WINE &amp; LIQUOR</t>
+          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77022</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21 MIDLAND AVE</t>
+          <t>10 NJ-17</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>RUTHERFORD</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1676,22 +1676,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:37 AM</t>
+          <t>10/07/2026 11:12 AM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1710,26 +1710,26 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>FOOD MART LIQUOR</t>
+          <t>LIQUOR FACTORY III SPARTA</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77001</t>
+          <t>230114</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>430 MARKET ST</t>
+          <t>41 WOODPORT ROAD</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1744,10 +1744,14 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1757,22 +1761,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:24 AM</t>
+          <t>10/07/2026 10:14 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1791,26 +1795,26 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
+          <t>SUPER SAVER LIQ</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>191408</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>545 BOULEVARD</t>
+          <t>322 HOWARD BLVD</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>MT ARLINGTON</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1825,10 +1829,14 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1838,22 +1846,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 11:37 AM</t>
+          <t>10/06/2026 03:33 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1876,22 +1884,22 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
+          <t>GARDEN LIQUORS (P)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>230427</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125 WATER ST</t>
+          <t>300 HARRISON AVE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1906,7 +1914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1923,22 +1931,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:59 AM</t>
+          <t>10/06/2026 02:35 PM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1961,22 +1969,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1991,7 +1999,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2008,22 +2016,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:15 AM</t>
+          <t>10/06/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2046,22 +2054,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2076,7 +2084,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2093,22 +2101,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 02:30 PM</t>
+          <t>10/06/2026 02:02 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2131,22 +2139,22 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>BOONTON LIQUOR LOCKER</t>
+          <t>SHOP RITE LIQ.(A)LODI</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>190208</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119 HAWKINS PL</t>
+          <t>150 MAIN STR</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>BOONTON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Cooler Door Wrap</t>
+          <t>POS, Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2178,22 +2186,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:49 AM</t>
+          <t>10/06/2026 11:40 AM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2212,26 +2220,26 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAIN STREET LIQUOR</t>
+          <t>M &amp; M WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>190913</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>340 S MAIN ST</t>
+          <t>429 MARKET ST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2246,14 +2254,10 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2263,17 +2267,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:02 AM</t>
+          <t>10/06/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2297,26 +2301,26 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>SAVERS CLUB LIQUOR LOCKER</t>
+          <t>ALL STAR WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>77022</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>314 CLIFTON AVE</t>
+          <t>21 MIDLAND AVE</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2331,14 +2335,10 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>TALKHOUSE ENCORE</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2348,22 +2348,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:39 AM</t>
+          <t>10/06/2026 09:37 AM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2382,26 +2382,26 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>FOOD MART LIQUOR</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>77001</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>430 MARKET ST</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2429,22 +2429,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:38 AM</t>
+          <t>10/06/2026 09:24 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2463,26 +2463,26 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>545 BOULEVARD</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2497,14 +2497,10 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2514,7 +2510,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 09:46 AM</t>
+          <t>10/05/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2524,7 +2520,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2552,22 +2548,22 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>SAM'S LIQ WINE (P)</t>
+          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>230427</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>325 W CLINTON ST</t>
+          <t>125 WATER ST</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>DOVER</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2599,22 +2595,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>10/05/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2637,27 +2633,27 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2684,22 +2680,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>10/05/2026 10:15 AM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2722,27 +2718,27 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2769,7 +2765,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/30/2026 02:30 PM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2779,12 +2775,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2807,27 +2803,27 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>BOONTON LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>119 HAWKINS PL</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>BOONTON</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2854,7 +2850,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/30/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2864,12 +2860,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2879,7 +2875,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2892,27 +2888,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>MAIN STREET LIQUOR</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>340 S MAIN ST</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2922,12 +2918,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -2939,7 +2935,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/30/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2949,12 +2945,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2977,22 +2973,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>SAVERS CLUB LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>314 CLIFTON AVE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3007,12 +3003,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3024,7 +3020,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/30/2026 10:39 AM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3034,12 +3030,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3062,27 +3058,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3092,14 +3088,10 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3109,7 +3101,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/30/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -3119,12 +3111,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3147,22 +3139,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3194,22 +3186,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3232,27 +3224,27 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3262,12 +3254,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3279,17 +3271,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3317,27 +3309,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3347,12 +3339,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3364,17 +3356,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3402,27 +3394,27 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3449,12 +3441,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3487,22 +3479,22 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3534,22 +3526,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3559,7 +3551,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3572,27 +3564,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3602,10 +3594,14 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="n"/>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3615,17 +3611,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3653,27 +3649,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3683,12 +3679,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3700,22 +3696,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3738,27 +3734,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3785,22 +3781,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3819,31 +3815,31 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3853,7 +3849,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -3870,17 +3866,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3904,31 +3900,31 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3938,7 +3934,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -3955,17 +3951,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3989,31 +3985,31 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4023,12 +4019,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>FAMOSA LAGER</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4040,17 +4036,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4074,31 +4070,31 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4108,10 +4104,14 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4121,12 +4121,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4155,26 +4155,26 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4206,17 +4206,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4240,31 +4240,31 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4274,14 +4274,10 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n"/>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4291,17 +4287,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4325,31 +4321,31 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4359,7 +4355,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4376,22 +4372,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4410,31 +4406,31 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4444,12 +4440,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -4461,12 +4457,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4499,22 +4495,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4529,12 +4525,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -4546,12 +4542,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4580,26 +4576,26 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4614,12 +4610,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -4631,12 +4627,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4665,26 +4661,26 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4699,7 +4695,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -4716,12 +4712,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4750,26 +4746,26 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4784,14 +4780,10 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n"/>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4801,12 +4793,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4839,22 +4831,22 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4886,12 +4878,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4920,21 +4912,21 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4954,10 +4946,14 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="n"/>
+          <t>ARNOLD PALMER SPIKED</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4967,22 +4963,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5001,31 +4997,31 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5035,7 +5031,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -5052,22 +5048,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5086,31 +5082,31 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5120,12 +5116,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -5137,22 +5133,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5171,31 +5167,31 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5205,12 +5201,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5222,17 +5218,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -5256,31 +5252,31 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5290,12 +5286,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -5307,22 +5303,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5341,31 +5337,31 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5375,7 +5371,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>PERONI NASTRO AZZURRO</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -5392,22 +5388,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5430,27 +5426,27 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5460,12 +5456,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -5477,22 +5473,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5511,31 +5507,31 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5562,22 +5558,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5600,27 +5596,27 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5630,14 +5626,10 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n"/>
       <c r="Q61" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5647,17 +5639,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5681,31 +5673,31 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5715,12 +5707,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5732,12 +5724,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5770,17 +5762,17 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5790,7 +5782,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5817,17 +5809,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5855,27 +5847,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5885,12 +5877,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -5902,12 +5894,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5940,22 +5932,22 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5970,10 +5962,14 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="n"/>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5983,12 +5979,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6021,17 +6017,17 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6041,7 +6037,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -6068,22 +6064,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6106,27 +6102,27 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -6136,7 +6132,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -6153,22 +6149,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6191,22 +6187,22 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6221,12 +6217,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6238,17 +6234,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6276,27 +6272,27 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6323,17 +6319,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6357,31 +6353,31 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6391,12 +6387,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6408,12 +6404,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -6446,27 +6442,27 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6493,17 +6489,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6531,27 +6527,27 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -6561,12 +6557,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6578,22 +6574,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6616,27 +6612,27 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6646,14 +6642,10 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n"/>
       <c r="Q73" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -6663,12 +6655,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6701,22 +6693,22 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6748,22 +6740,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6786,27 +6778,27 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6816,7 +6808,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -6833,22 +6825,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6867,31 +6859,31 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6901,12 +6893,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -6918,17 +6910,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6956,27 +6948,27 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7003,12 +6995,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -7041,22 +7033,22 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -7088,12 +7080,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -7126,27 +7118,27 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -7173,17 +7165,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -7211,27 +7203,27 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7258,22 +7250,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7296,27 +7288,27 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -7326,12 +7318,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS GINGER LIME</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -7343,22 +7335,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7381,27 +7373,27 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -7411,12 +7403,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS RASPBERRY ROSE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7428,22 +7420,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:07 PM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -7466,27 +7458,27 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -7496,12 +7488,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>POP SIPS VARIETY 8PK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>PASSION TREE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -7513,17 +7505,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7547,31 +7539,31 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -7581,7 +7573,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -7598,22 +7590,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/15/2026 12:05 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7636,22 +7628,22 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7666,7 +7658,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -7683,22 +7675,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 09:50 AM</t>
+          <t>09/21/2026 10:32 AM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7717,31 +7709,31 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (A)HILLSDAL</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>73008</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>371 BROADWAY</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>HILLSDALE</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7751,12 +7743,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -7768,7 +7760,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:38 AM</t>
+          <t>09/17/2026 12:44 PM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -7778,12 +7770,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7806,27 +7798,27 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>WINEMART DISCOUNT</t>
+          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>700 BROADWAY SUITE 42</t>
+          <t>109 MAIN ST</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7836,12 +7828,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>NIGHT SHIFT BREWING</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -7853,22 +7845,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:36 AM</t>
+          <t>09/16/2026 01:16 PM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7891,22 +7883,22 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7921,12 +7913,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING CO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -7938,17 +7930,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7976,22 +7968,22 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -8006,12 +7998,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>POP SIPS GINGER LIME</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -8023,17 +8015,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -8061,22 +8053,22 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -8091,12 +8083,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>CORONA LIGHT</t>
+          <t>POP SIPS RASPBERRY ROSE</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8108,17 +8100,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -8146,22 +8138,22 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -8176,12 +8168,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>CORONA PREMIER</t>
+          <t>POP SIPS VARIETY 8PK</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>PASSION TREE</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -8193,17 +8185,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:35 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -8231,22 +8223,22 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>GARDEN STATE DELI (A)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>135 OAKLAND AVE</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>CLOSTER</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -8261,12 +8253,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8278,17 +8270,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>09/14/2026 07:31 AM</t>
+          <t>09/15/2026 12:05 PM</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -8316,22 +8308,22 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD WINE AND LIQUORS</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>725 BROADWAY</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>WESTWOOD</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -8346,12 +8338,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MILLER LITE BEER</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -8363,22 +8355,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>09/11/2026 08:55 AM</t>
+          <t>09/14/2026 09:50 AM</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8397,26 +8389,26 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>HOME WINE LIQUOR (PASSAIC)</t>
+          <t>SHOP RITE LIQ (A)HILLSDAL</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>593 MAIN AVE</t>
+          <t>371 BROADWAY</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>HILLSDALE</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -8431,12 +8423,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8448,22 +8440,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>09/10/2026 11:46 AM</t>
+          <t>09/14/2026 07:38 AM</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -8486,27 +8478,27 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>WINEMART DISCOUNT</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>74005</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>700 BROADWAY SUITE 42</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -8516,12 +8508,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>NIGHT SHIFT X CAPE MAY BREWBERRY</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>NIGHT SHIFT BREWING</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -8533,17 +8525,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:36 AM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -8567,31 +8559,31 @@
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -8618,17 +8610,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -8656,27 +8648,27 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -8686,12 +8678,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -8703,17 +8695,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -8741,27 +8733,27 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -8771,12 +8763,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
+          <t>CORONA LIGHT</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -8788,17 +8780,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -8826,27 +8818,27 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -8856,12 +8848,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
+          <t>CORONA PREMIER</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -8873,17 +8865,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:35 AM</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -8911,27 +8903,27 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>GARDEN STATE DELI (A)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>62001</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>135 OAKLAND AVE</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>CLOSTER</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8941,12 +8933,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -8958,17 +8950,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/14/2026 07:31 AM</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -8996,27 +8988,27 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>WESTWOOD WINE AND LIQUORS</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>74009</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>725 BROADWAY</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WESTWOOD</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -9026,12 +9018,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
@@ -9043,22 +9035,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 12:40 PM</t>
+          <t>09/11/2026 08:55 AM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -9077,31 +9069,31 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>HOME WINE LIQUOR (PASSAIC)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>593 MAIN AVE</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -9111,12 +9103,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q102" s="3" t="inlineStr">
@@ -9128,22 +9120,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:37 AM</t>
+          <t>09/10/2026 11:46 AM</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -9166,27 +9158,27 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>WINELAND</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>247 DEGRAW AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>TEANECK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -9196,10 +9188,14 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P103" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -9209,17 +9205,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -9243,31 +9239,31 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -9277,12 +9273,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>ATHLETIC BREWING CO</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q104" s="3" t="inlineStr">
@@ -9294,17 +9290,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:28 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -9332,27 +9328,27 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK WINE/SPIRITS</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>23 WYCKOFF AVE</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>WALDWICK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -9362,12 +9358,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q105" s="3" t="inlineStr">
@@ -9379,22 +9375,22 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 12:17 PM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -9417,27 +9413,27 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>390 MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -9447,12 +9443,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>SUN CRUISER ICED TEA + VODKA, CLASSIC ICED TEA</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q106" s="3" t="inlineStr">
@@ -9464,22 +9460,22 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:37 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -9502,27 +9498,27 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -9532,12 +9528,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>MODELO CHELADA</t>
+          <t>SUN CRUISER ICED TEA + VODKA, HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q107" s="3" t="inlineStr">
@@ -9549,22 +9545,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:35 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -9587,27 +9583,27 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -9617,12 +9613,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
+          <t>SUN CRUISER ICED TEA VODKA VARIETY 18 PACK</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>VINAIO IMPORTS LTD</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q108" s="3" t="inlineStr">
@@ -9634,22 +9630,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:34 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -9672,27 +9668,27 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -9702,12 +9698,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>MODELO ORO</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q109" s="3" t="inlineStr">
@@ -9719,22 +9715,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/08/2026 11:32 AM</t>
+          <t>09/09/2026 12:40 PM</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Derrick laws</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -9753,31 +9749,31 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>THE LIQUOR SHOP</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>498 E 30TH STREET</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -9787,12 +9783,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q110" s="3" t="inlineStr">
@@ -9804,7 +9800,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:34 AM</t>
+          <t>09/09/2026 10:37 AM</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -9842,22 +9838,22 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINELAND</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>247 DEGRAW AVE</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>TEANECK</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -9872,14 +9868,10 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
-        </is>
-      </c>
-      <c r="P111" s="2" t="inlineStr">
-        <is>
-          <t>DRINK CARBLISS</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="n"/>
       <c r="Q111" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -9889,7 +9881,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:33 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -9899,12 +9891,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -9927,22 +9919,22 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -9957,7 +9949,7 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
@@ -9974,7 +9966,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:32 AM</t>
+          <t>09/08/2026 12:28 PM</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -9984,12 +9976,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -10012,22 +10004,22 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WALDWICK WINE/SPIRITS</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>23 WYCKOFF AVE</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WALDWICK</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -10042,7 +10034,7 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
@@ -10059,7 +10051,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -10069,12 +10061,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10097,22 +10089,22 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAPHAEL &amp; ANGEL LIQ (A)</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>390 MAIN ST</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -10127,12 +10119,12 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q114" s="3" t="inlineStr">
@@ -10144,22 +10136,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:31 AM</t>
+          <t>09/08/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -10182,22 +10174,22 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -10212,7 +10204,7 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>MODELO CHELADA</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
@@ -10229,22 +10221,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:30 AM</t>
+          <t>09/08/2026 11:35 AM</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -10267,22 +10259,22 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -10297,12 +10289,12 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>CERVEZA REPUBLICA LA TUYA 5.0 LA DURA</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>VINAIO IMPORTS LTD</t>
         </is>
       </c>
       <c r="Q116" s="3" t="inlineStr">
@@ -10314,22 +10306,22 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:29 AM</t>
+          <t>09/08/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -10352,22 +10344,22 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -10382,12 +10374,12 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ORO</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q117" s="3" t="inlineStr">
@@ -10399,22 +10391,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 11:11 AM</t>
+          <t>09/08/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Derrick laws</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -10437,22 +10429,22 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+          <t>THE LIQUOR SHOP</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>21-00 MAPLE AVE</t>
+          <t>498 E 30TH STREET</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -10467,12 +10459,12 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q118" s="3" t="inlineStr">
@@ -10484,12 +10476,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:31 AM</t>
+          <t>09/03/2026 11:34 AM</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -10522,22 +10514,22 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -10569,12 +10561,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:30 AM</t>
+          <t>09/03/2026 11:33 AM</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -10607,22 +10599,22 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -10637,12 +10629,12 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q120" s="3" t="inlineStr">
@@ -10654,12 +10646,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:29 AM</t>
+          <t>09/03/2026 11:32 AM</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -10692,22 +10684,22 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -10722,12 +10714,12 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
@@ -10739,12 +10731,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -10777,22 +10769,22 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -10807,12 +10799,12 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q122" s="3" t="inlineStr">
@@ -10824,12 +10816,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 10:28 AM</t>
+          <t>09/03/2026 11:31 AM</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -10862,22 +10854,22 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -10892,12 +10884,12 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>MILLER LITE BEER</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr">
@@ -10909,83 +10901,763 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>09/03/2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>CAPE MAY BREWING COMPANY</t>
+        </is>
+      </c>
+      <c r="Q124" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>76010</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>66 MARKET ST</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>SADDLE BROOK</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q125" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 11:11 AM</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Mike Ast</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN WINE &amp; SPIRITS</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>81006</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>21-00 MAPLE AVE</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>FAIR LAWN</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="Q126" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:31 AM</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>CORONA EXTRA</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q128" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>MODELO ESPECIAL</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>CONSTELLATION BRANDS</t>
+        </is>
+      </c>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>COORS LIGHT BEER</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:28 AM</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Chris Payton</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Michael Engel</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON DISC LIQ (A)</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>MBO</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>MILLER LITE BEER</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
           <t>09/03/2026 10:27 AM</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Chris Payton</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Michael Engel</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Ashley Furman</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Sales Rep</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Feature Activation</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="n">
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Ashley Furman</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>25045</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
+      <c r="K132" s="2" t="inlineStr">
         <is>
           <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
-      <c r="L124" s="2" t="inlineStr">
+      <c r="L132" s="2" t="inlineStr">
         <is>
           <t>CLIFTON</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="M132" s="2" t="inlineStr">
         <is>
           <t>MBO</t>
         </is>
       </c>
-      <c r="N124" s="2" t="inlineStr">
-        <is>
-          <t>Cooler Door Wrap</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Cooler Door Wrap</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>MODELO CHELADA</t>
         </is>
       </c>
-      <c r="P124" s="2" t="inlineStr">
+      <c r="P132" s="2" t="inlineStr">
         <is>
           <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
-      <c r="Q124" s="3" t="inlineStr">
+      <c r="Q132" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -11116,6 +11788,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/pos_cooler_door_promos.xlsx
+++ b/MPOs/off-prem/pos_cooler_door_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q132"/>
+  <dimension ref="A1:Q135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/15/2026 12:17 PM</t>
+          <t>10/19/2026 02:03 PM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -625,26 +625,26 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>GARDEN STATE FOOD&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>666 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 01:34 PM</t>
+          <t>10/19/2026 01:13 PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -706,31 +706,31 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>W E BEVERAGE (A)</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>52019</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>91 W PALISADE AVE</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ENGLEWOOD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -740,10 +740,14 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n"/>
+          <t>WHITE CLAW SURGE PINEAPPLE</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>MARK ANTHONY GROUP</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -753,7 +757,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 01:34 PM</t>
+          <t>10/19/2026 12:56 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -763,12 +767,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mike Ast</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -787,26 +791,26 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>LINCOLN PARK FINE WINES &amp; SPIRITS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60 BEAVERBROOK ROAD</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LINCOLN PARK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -821,12 +825,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC RUN WILD NA IPA</t>
+          <t>WHITE CLAW SURGE GREEN APPLE</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>ATHLETIC BREWING COMPANY</t>
+          <t>MARK ANTHONY GROUP</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -838,17 +842,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 11:42 AM</t>
+          <t>10/15/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -872,26 +876,26 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>CARISMA LIQ &amp; GROC (P)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>230 VREELAND AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -906,14 +910,10 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>MONACO BLUE CRUSH</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -923,17 +923,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 11:28 AM</t>
+          <t>10/14/2026 01:34 PM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -957,31 +957,31 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>EXQUISITE W &amp; L (A)</t>
+          <t>W E BEVERAGE (A)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>52019</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>215 MAIN ST</t>
+          <t>91 W PALISADE AVE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -991,14 +991,10 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1008,22 +1004,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 11:28 AM</t>
+          <t>10/14/2026 01:34 PM</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Mike Ast</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1046,22 +1042,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>EXQUISITE W &amp; L (A)</t>
+          <t>LINCOLN PARK FINE WINES &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>215 MAIN ST</t>
+          <t>60 BEAVERBROOK ROAD</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>LINCOLN PARK</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1076,12 +1072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>ATHLETIC RUN WILD NA IPA</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>ATHLETIC BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1093,22 +1089,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 11:28 AM</t>
+          <t>10/14/2026 11:42 AM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1131,22 +1127,22 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>EXQUISITE W &amp; L (A)</t>
+          <t>CARISMA LIQ &amp; GROC (P)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>215 MAIN ST</t>
+          <t>230 VREELAND AVE</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1161,7 +1157,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED VARIETY</t>
+          <t>MONACO BLUE CRUSH</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1178,22 +1174,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/14/2026 07:25 AM</t>
+          <t>10/14/2026 11:28 AM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Shane Barreca</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1216,22 +1212,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>CORK &amp; KEG (A)</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75004</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89 KINDERKAMACK RD</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>EMERSON</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1246,12 +1242,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1263,12 +1259,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026 02:43 PM</t>
+          <t>10/14/2026 11:28 AM</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1301,22 +1297,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1331,10 +1327,14 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n"/>
+          <t>ARNOLD PALMER SPIKED</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1344,12 +1344,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/12/2026 02:43 PM</t>
+          <t>10/14/2026 11:28 AM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1382,22 +1382,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>CARBLISS</t>
+          <t>SIMPLY SPIKED VARIETY</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>DRINK CARBLISS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1429,22 +1429,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 12:15 PM</t>
+          <t>10/14/2026 07:25 AM</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Shane Barreca</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1467,22 +1467,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>CORK &amp; KEG (A)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>75004</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>89 KINDERKAMACK RD</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>EMERSON</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>MONACO LIME CRUSH</t>
+          <t>SUN CRUISERS RTD</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1514,22 +1514,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/08/2026 11:49 AM</t>
+          <t>10/12/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1548,26 +1548,26 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>COBBLESTONE HILL DELI</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>287 BROAD ST</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1595,22 +1595,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 02:08 PM</t>
+          <t>10/12/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1629,26 +1629,26 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10 NJ-17</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>RUTHERFORD</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1663,10 +1663,14 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n"/>
+          <t>CARBLISS</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>DRINK CARBLISS</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1676,22 +1680,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 11:12 AM</t>
+          <t>10/08/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1714,22 +1718,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR FACTORY III SPARTA</t>
+          <t>LEGACY BAR &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>230114</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41 WOODPORT ROAD</t>
+          <t>1019 MCBRIDE AVE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>WOODLAND PARK</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1744,7 +1748,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MONACO LIME CRUSH</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1761,22 +1765,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026 10:14 AM</t>
+          <t>10/08/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1795,26 +1799,26 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>SUPER SAVER LIQ</t>
+          <t>COBBLESTONE HILL DELI</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>191408</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>322 HOWARD BLVD</t>
+          <t>287 BROAD ST</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>MT ARLINGTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1829,14 +1833,10 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1846,22 +1846,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 03:33 PM</t>
+          <t>10/07/2026 02:08 PM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1880,26 +1880,26 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>GARDEN LIQUORS (P)</t>
+          <t>BOTTLE REPUBLIC (RUTHERFORD)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>300 HARRISON AVE</t>
+          <t>10 NJ-17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RUTHERFORD</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1914,14 +1914,10 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -1931,22 +1927,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:35 PM</t>
+          <t>10/07/2026 11:12 AM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1969,22 +1965,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE DISCOUNT LIQUOR</t>
+          <t>LIQUOR FACTORY III SPARTA</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>230114</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>183 ROUTE 46 WEST</t>
+          <t>41 WOODPORT ROAD</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1999,7 +1995,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2016,22 +2012,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:34 PM</t>
+          <t>10/07/2026 10:14 AM</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2054,22 +2050,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE DISCOUNT LIQUOR</t>
+          <t>SUPER SAVER LIQ</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>191408</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>183 ROUTE 46 WEST</t>
+          <t>322 HOWARD BLVD</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MT ARLINGTON</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2084,7 +2080,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2101,12 +2097,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 02:02 PM</t>
+          <t>10/06/2026 03:33 PM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2139,17 +2135,17 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ.(A)LODI</t>
+          <t>GARDEN LIQUORS (P)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>150 MAIN STR</t>
+          <t>300 HARRISON AVE</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2164,12 +2160,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>POS, Cooler Door Wrap</t>
+          <t>Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2186,22 +2182,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 11:40 AM</t>
+          <t>10/06/2026 02:35 PM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2220,26 +2216,26 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>M &amp; M WINE &amp; SPIRITS</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>429 MARKET ST</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2254,10 +2250,14 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2267,22 +2267,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 11:02 AM</t>
+          <t>10/06/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2301,26 +2301,26 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>ALL STAR WINE &amp; LIQUOR</t>
+          <t>BUY RITE DISCOUNT LIQUOR</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>77022</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21 MIDLAND AVE</t>
+          <t>183 ROUTE 46 WEST</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2335,10 +2335,14 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2348,22 +2352,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:37 AM</t>
+          <t>10/06/2026 02:02 PM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2382,26 +2386,26 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>FOOD MART LIQUOR</t>
+          <t>SHOP RITE LIQ.(A)LODI</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>77001</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>430 MARKET ST</t>
+          <t>150 MAIN STR</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>ELMWOOD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2411,15 +2415,19 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Cooler Door Wrap</t>
+          <t>POS, Cooler Door Wrap</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2429,12 +2437,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:24 AM</t>
+          <t>10/06/2026 11:40 AM</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2463,21 +2471,21 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
+          <t>M &amp; M WINE &amp; SPIRITS</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>545 BOULEVARD</t>
+          <t>429 MARKET ST</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2510,22 +2518,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 11:37 AM</t>
+          <t>10/06/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2544,26 +2552,26 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
+          <t>ALL STAR WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>230427</t>
+          <t>77022</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>125 WATER ST</t>
+          <t>21 MIDLAND AVE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2578,14 +2586,10 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2595,22 +2599,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:59 AM</t>
+          <t>10/06/2026 09:37 AM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2629,26 +2633,26 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
+          <t>FOOD MART LIQUOR</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>230412</t>
+          <t>77001</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17 HAMPTON HOUSE ROAD</t>
+          <t>430 MARKET ST</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2663,14 +2667,10 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2680,22 +2680,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026 10:15 AM</t>
+          <t>10/06/2026 09:24 AM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2714,26 +2714,26 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>BIRCHWOOD LIQ &amp; DELI (Z)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>545 BOULEVARD</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>ELMWOOD PARK</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2748,14 +2748,10 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n"/>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -2765,7 +2761,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 02:30 PM</t>
+          <t>10/05/2026 11:37 AM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2775,7 +2771,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2803,22 +2799,22 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>BOONTON LIQUOR LOCKER</t>
+          <t>SHOPRITE WINE &amp; SPIRITS OF NEWTON#830</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>190208</t>
+          <t>230427</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>119 HAWKINS PL</t>
+          <t>125 WATER ST</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>BOONTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2850,7 +2846,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:49 AM</t>
+          <t>10/05/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2860,7 +2856,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2888,22 +2884,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MAIN STREET LIQUOR</t>
+          <t>USA WINE TRADERS CLUB OF NEWTON (A)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>190913</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>340 S MAIN ST</t>
+          <t>17 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2935,22 +2931,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 11:02 AM</t>
+          <t>10/05/2026 10:15 AM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2973,22 +2969,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>SAVERS CLUB LIQUOR LOCKER</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>314 CLIFTON AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3003,12 +2999,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE VARIETY PACK</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>TALKHOUSE ENCORE</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -3020,12 +3016,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:39 AM</t>
+          <t>09/30/2026 02:30 PM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3058,22 +3054,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>BOONTON LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>119 HAWKINS PL</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>WHARTON</t>
+          <t>BOONTON</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3088,10 +3084,14 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="n"/>
+          <t>KEYSTONE ICE</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3101,12 +3101,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 10:38 AM</t>
+          <t>09/30/2026 11:49 AM</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3139,17 +3139,17 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>WHARTON LIQUOR STORE</t>
+          <t>MAIN STREET LIQUOR</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>41 N MAIN ST</t>
+          <t>340 S MAIN ST</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3186,22 +3186,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/30/2026 09:46 AM</t>
+          <t>09/30/2026 11:02 AM</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Klejdi Lamo</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>SAM'S LIQ WINE (P)</t>
+          <t>SAVERS CLUB LIQUOR LOCKER</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>325 W CLINTON ST</t>
+          <t>314 CLIFTON AVE</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>DOVER</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TALKHOUSE ENCORE VARIETY PACK</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>TALKHOUSE ENCORE</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/29/2026 12:30 PM</t>
+          <t>09/30/2026 10:39 AM</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>BOTTLE KING (A) GLEN ROCK</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>909 PROSPECT ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3339,14 +3339,10 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -3356,22 +3352,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 02:29 PM</t>
+          <t>09/30/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3394,27 +3390,27 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WHARTON LIQUOR STORE</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>190907</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>41 N MAIN ST</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WHARTON</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3441,7 +3437,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:25 PM</t>
+          <t>09/30/2026 09:46 AM</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3451,12 +3447,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Klejdi Lamo</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3479,27 +3475,27 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>CITY SUPERMARKET</t>
+          <t>SAM'S LIQ WINE (P)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>190802</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>289 BERGEN BLVD</t>
+          <t>325 W CLINTON ST</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>DOVER</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3526,22 +3522,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 12:16 PM</t>
+          <t>09/29/2026 12:30 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3551,7 +3547,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3564,22 +3560,22 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS VINEYARD (A)</t>
+          <t>BOTTLE KING (A) GLEN ROCK</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>875 BLOOMFIELD AVE</t>
+          <t>909 PROSPECT ST</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3594,12 +3590,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -3611,17 +3607,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:43 AM</t>
+          <t>09/28/2026 02:29 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3649,27 +3645,27 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>BUY RITE OF FAIRVIEW</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>201 BROAD AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3679,12 +3675,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>CORONA EXTRA</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -3696,17 +3692,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 11:03 AM</t>
+          <t>09/28/2026 12:25 PM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3734,27 +3730,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>DELI MART (A)</t>
+          <t>CITY SUPERMARKET</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>789 MAIN ST</t>
+          <t>289 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3781,17 +3777,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:59 AM</t>
+          <t>09/28/2026 12:16 PM</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3806,7 +3802,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3819,27 +3815,27 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>LUIGI'S LIQUOR (A)</t>
+          <t>SHOPPERS VINEYARD (A)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>175 JEFFERSON ST</t>
+          <t>875 BLOOMFIELD AVE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3849,12 +3845,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -3866,17 +3862,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:48 AM</t>
+          <t>09/28/2026 11:43 AM</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3904,27 +3900,27 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>BUY RITE OF FAIRVIEW</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>201 BROAD AVE</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3951,12 +3947,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:40 AM</t>
+          <t>09/28/2026 11:03 AM</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3989,17 +3985,17 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>DELI MART (A)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>789 MAIN ST</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4019,12 +4015,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>FAMOSA LAGER</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4036,22 +4032,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:38 AM</t>
+          <t>09/28/2026 10:59 AM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4074,27 +4070,27 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>GEORGE'S LIQ</t>
+          <t>LUIGI'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>130 ANDERSON ST</t>
+          <t>175 JEFFERSON ST</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>HACKENSACK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4121,17 +4117,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 10:25 AM</t>
+          <t>09/28/2026 10:48 AM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4159,27 +4155,27 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>467 ALLWOOD RD</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4189,12 +4185,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>CORONA EXTRA</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4206,12 +4202,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:40 AM</t>
+          <t>09/28/2026 10:40 AM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4244,22 +4240,22 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -4274,10 +4270,14 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n"/>
+          <t>FAMOSA LAGER</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>CENTRAL BEER IMPORT &amp; EXPORT FAMOSA</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4287,12 +4287,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09/28/2026 09:36 AM</t>
+          <t>09/28/2026 10:38 AM</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4325,22 +4325,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>GEORGE'S LIQ</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>130 ANDERSON ST</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>HACKENSACK</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4372,22 +4372,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 03:15 PM</t>
+          <t>09/28/2026 10:25 AM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4410,27 +4410,27 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
+          <t>STEW LEONARD'S WINES &amp; SPIRITS OF CLIFTON</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>292-294 MARKET STREET</t>
+          <t>467 ALLWOOD RD</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4457,17 +4457,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:43 PM</t>
+          <t>09/28/2026 09:40 AM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4491,31 +4491,31 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4525,14 +4525,10 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n"/>
       <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4542,17 +4538,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:42 PM</t>
+          <t>09/28/2026 09:36 AM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4576,31 +4572,31 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4610,12 +4606,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -4627,22 +4623,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 02:39 PM</t>
+          <t>09/23/2026 03:15 PM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4661,21 +4657,21 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>SUPER WINE WAREHSE(P)PATE</t>
+          <t>COSTAMBAR BAR &amp; LIQUOR CORP.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>42 E 30TH ST</t>
+          <t>292-294 MARKET STREET</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4685,7 +4681,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4695,7 +4691,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>BLUE MOON BELGIAN WHITE ALE</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -4712,12 +4708,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 01:20 PM</t>
+          <t>09/23/2026 02:43 PM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4746,26 +4742,26 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4780,10 +4776,14 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -4793,12 +4793,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:49 PM</t>
+          <t>09/23/2026 02:42 PM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4827,26 +4827,26 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ(A) FAIR LWN</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>35-07 BROADWAY</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>FAIR LAWN</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -4878,12 +4878,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 02:39 PM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4912,26 +4912,26 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SUPER WINE WAREHSE(P)PATE</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>42 E 30TH ST</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED</t>
+          <t>BLUE MOON BELGIAN WHITE ALE</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 01:20 PM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4997,26 +4997,26 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -5031,14 +5031,10 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>SIMPLY SPIKED LEMONADE</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n"/>
       <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5048,12 +5044,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:15 PM</t>
+          <t>09/23/2026 12:49 PM</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5086,22 +5082,22 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE LIQ(A) FAIR LWN</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>35-07 BROADWAY</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FAIR LAWN</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -5133,12 +5129,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:14 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5167,7 +5163,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -5201,12 +5197,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>TRULY HARD SELTZER</t>
+          <t>ARNOLD PALMER SPIKED</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5218,12 +5214,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:12 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5252,7 +5248,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -5286,12 +5282,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY IPA</t>
+          <t>SIMPLY SPIKED LEMONADE</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>CAPE MAY BREWING COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -5303,12 +5299,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:10 PM</t>
+          <t>09/23/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5337,7 +5333,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -5371,12 +5367,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>PERONI NASTRO AZZURRO</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5388,12 +5384,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:09 PM</t>
+          <t>09/23/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5422,7 +5418,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -5473,12 +5469,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 12:07 PM</t>
+          <t>09/23/2026 12:12 PM</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5541,12 +5537,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>CAPE MAY IPA</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CAPE MAY BREWING COMPANY</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5558,12 +5554,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/23/2026 10:52 AM</t>
+          <t>09/23/2026 12:10 PM</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5592,21 +5588,21 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>396 RT 17 NORTH</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -5626,10 +5622,14 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="n"/>
+          <t>PERONI NASTRO AZZURRO</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
+        </is>
+      </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5639,22 +5639,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 02:09 PM</t>
+          <t>09/23/2026 12:09 PM</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5677,27 +5677,27 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>SCHULMAN'S (P) DELI</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>521 PARK AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TRULY HARD SELTZER</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -5724,22 +5724,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:37 PM</t>
+          <t>09/23/2026 12:07 PM</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5758,31 +5758,31 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>CARABALLO'S</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>495 MARKET STREET</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -5809,22 +5809,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 01:01 PM</t>
+          <t>09/23/2026 10:52 AM</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5847,27 +5847,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>ALTIERO LIQUORS</t>
+          <t>PRIME WINE CELLAR LIQUOR &amp; BEER</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>498 ELLISON ST.</t>
+          <t>396 RT 17 NORTH</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5877,14 +5877,10 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n"/>
       <c r="Q64" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -5894,22 +5890,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:52 PM</t>
+          <t>09/22/2026 02:09 PM</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5932,27 +5928,27 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
+          <t>SCHULMAN'S (P) DELI</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>153 BERGEN BLVD</t>
+          <t>521 PARK AVE</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>FAIRVIEW</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5962,12 +5958,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>MODELO ESPECIAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>CONSTELLATION BRANDS</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -5979,12 +5975,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:35 PM</t>
+          <t>09/22/2026 01:37 PM</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6017,17 +6013,17 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>RIVERSIDE LIQUORS (PATERSON)</t>
+          <t>CARABALLO'S</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>402 RIVER ST</t>
+          <t>495 MARKET STREET</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6037,7 +6033,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -6064,12 +6060,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:17 PM</t>
+          <t>09/22/2026 01:01 PM</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6102,17 +6098,17 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>GENE'S LIQUOR</t>
+          <t>ALTIERO LIQUORS</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>26 N STRAIGHT ST</t>
+          <t>498 ELLISON ST.</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -6149,22 +6145,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:15 PM</t>
+          <t>09/22/2026 12:52 PM</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6187,22 +6183,22 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>BOULEVARD LIQ.(FAIRVIEW)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>153 BERGEN BLVD</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>FAIRVIEW</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6217,12 +6213,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>MODELO ESPECIAL</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>CONSTELLATION BRANDS</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6234,17 +6230,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 12:14 PM</t>
+          <t>09/22/2026 12:35 PM</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6272,27 +6268,27 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>RIVERSIDE LIQUORS (PATERSON)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>402 RIVER ST</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -6319,17 +6315,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:45 AM</t>
+          <t>09/22/2026 12:17 PM</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6353,31 +6349,31 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
+          <t>GENE'S LIQUOR</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>17 SCHUYLER AVE</t>
+          <t>26 N STRAIGHT ST</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6387,12 +6383,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>SUN CRUISERS RTD</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6404,17 +6400,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:29 AM</t>
+          <t>09/22/2026 12:15 PM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -6442,27 +6438,27 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>JOE'S LIQUOR (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>328 11TH AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6472,12 +6468,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -6489,12 +6485,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:07 AM</t>
+          <t>09/22/2026 12:14 PM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6527,22 +6523,22 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR SHED</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>740 RIDGE ROAD</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6557,12 +6553,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>TWISTED TEA ORIGINAL</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>MOLSON COORS BEVERAGE COMPANY</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6574,22 +6570,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 11:04 AM</t>
+          <t>09/22/2026 11:45 AM</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6608,26 +6604,26 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
+          <t>METRO LIQUORS (NORTH ARLINGTON)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>341 GORGE RD.</t>
+          <t>17 SCHUYLER AVE</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -6642,10 +6638,14 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>MONACO</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="n"/>
+          <t>SUN CRUISERS RTD</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -6655,12 +6655,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:53 AM</t>
+          <t>09/22/2026 11:29 AM</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6693,17 +6693,17 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
+          <t>JOE'S LIQUOR (A)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>192 E 16TH ST</t>
+          <t>328 11TH AVE</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6740,22 +6740,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:07 AM</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>LIQUOR SHED</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>740 RIDGE ROAD</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>COORS LIGHT BEER</t>
+          <t>TWISTED TEA ORIGINAL</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -6825,12 +6825,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09/22/2026 10:42 AM</t>
+          <t>09/22/2026 11:04 AM</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6863,17 +6863,17 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>METRO LIQUOR (CLIFFSIDE PARK)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>341 GORGE RD.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -6893,14 +6893,10 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="n"/>
       <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
@@ -6910,12 +6906,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:54 PM</t>
+          <t>09/22/2026 10:53 AM</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6948,27 +6944,27 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>#1 LIQRS (P)</t>
+          <t>BOMBOLON LIQUOR &amp; GROCERY</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>130 HOWE AVE</t>
+          <t>192 E 16TH ST</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6995,22 +6991,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 02:34 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7033,27 +7029,27 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>JOHNNY'S LIQS (P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>370 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7063,7 +7059,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>COORS LIGHT BEER</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -7080,22 +7076,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:56 PM</t>
+          <t>09/22/2026 10:42 AM</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -7118,27 +7114,27 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MONROE WINE &amp; LIQ(P)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>199 MONROE ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -7148,12 +7144,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>MOLSON COORS BEVERAGE COMPANY</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -7165,12 +7161,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:46 PM</t>
+          <t>09/21/2026 02:54 PM</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -7203,17 +7199,17 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>BROADWAY W&amp;L</t>
+          <t>#1 LIQRS (P)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>62 BROADWAY</t>
+          <t>130 HOWE AVE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7223,7 +7219,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7250,12 +7246,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 01:23 PM</t>
+          <t>09/21/2026 02:34 PM</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -7288,17 +7284,17 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>SUNNY'S LIQS.(P)</t>
+          <t>JOHNNY'S LIQS (P)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>413 MONROE ST</t>
+          <t>370 MONROE ST</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -7308,7 +7304,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Incentive, MBO</t>
+          <t>MBO, Incentive</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -7335,12 +7331,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:58 PM</t>
+          <t>09/21/2026 01:56 PM</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -7373,17 +7369,17 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>MONROE WINE &amp; LIQ(P)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>199 MONROE ST</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7420,12 +7416,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 12:38 PM</t>
+          <t>09/21/2026 01:46 PM</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7458,17 +7454,17 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>BROADWAY W&amp;L</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>62 BROADWAY</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -7478,7 +7474,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>MBO, Incentive</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -7505,22 +7501,22 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:54 AM</t>
+          <t>09/21/2026 01:23 PM</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7539,31 +7535,31 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>SUNNY'S LIQS.(P)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>413 MONROE ST</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -7573,7 +7569,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
+          <t>KEYSTONE ICE</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -7590,17 +7586,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:45 AM</t>
+          <t>09/21/2026 12:58 PM</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -7628,27 +7624,27 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>MBO</t>
+          <t>Incentive, MBO</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -7675,12 +7671,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/21/2026 10:32 AM</t>
+          <t>09/21/2026 12:38 PM</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7713,22 +7709,22 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>LEGACY BAR &amp; LIQUOR</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>1019 MCBRIDE AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7760,22 +7756,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/17/2026 12:44 PM</t>
+          <t>09/21/2026 10:54 AM</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7794,31 +7790,31 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>INTENSITY LOUNGE/ANGIE'S LIQUORS</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>109 MAIN ST</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Incentive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7828,7 +7824,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>KEYSTONE ICE</t>
+          <t>ARNOLD PALMER SPIKED HALF &amp; HALF</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -7845,12 +7841,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>09/16/2026 01:16 PM</t>
+          <t>09/21/2026 10:45 AM</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>